--- a/output/final/geo/geo distributors (status checked)/geo_commercial_drone_services_verified_distributors.xlsx
+++ b/output/final/geo/geo distributors (status checked)/geo_commercial_drone_services_verified_distributors.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$5:$U$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$5:$U$210</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Companies'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U211"/>
+  <dimension ref="A1:U210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -647,7 +647,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Distributors listed: 206     |     Headquarter countries: 1     |     Acquired by another group (named in the company name): 4</t>
+          <t>Distributors listed: 205     |     Headquarter countries: 1     |     Acquired by another group (named in the company name): 4</t>
         </is>
       </c>
     </row>
@@ -11568,16 +11568,16 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>Vayu Drone Technologies Pvt Ltd</t>
+          <t>Fresco Drone Services LLP</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>linkedin.com</t>
+          <t>zaubacorp.com</t>
         </is>
       </c>
       <c r="D134" s="11" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
@@ -11596,45 +11596,53 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Joint Venture</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>Volumetric mine surveying; cadastral overlays; agricultural pesticide spraying operations</t>
+          <t>Commercial drone field work; industrial aerial imaging; site inspection workflows</t>
         </is>
       </c>
       <c r="K134" s="14" t="inlineStr">
         <is>
-          <t>Turnkey remote sensing mapping overlays, asset tagging, and regulatory flight training workshop coordination</t>
+          <t>Local regional service delivery for infrastructure, layout surveying, and utilities across Telangana corridors</t>
         </is>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>Multispectral crop sensors, thermal utility payload tools, DGPS structural controls, and high-resolution ortho analytics</t>
+          <t>High-definition orthomosaic mapping arrays, topography point cloud outputs, and localized agricultural spraying</t>
         </is>
       </c>
       <c r="M134" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N134" s="14" t="inlineStr"/>
       <c r="O134" s="14" t="inlineStr"/>
-      <c r="P134" s="14" t="inlineStr"/>
+      <c r="P134" s="13" t="inlineStr">
+        <is>
+          <t>mahesh.kasani@gmail.com</t>
+        </is>
+      </c>
       <c r="Q134" s="14" t="inlineStr"/>
       <c r="R134" s="14" t="inlineStr"/>
       <c r="S134" s="13" t="inlineStr">
         <is>
-          <t>linkedin.com</t>
-        </is>
-      </c>
-      <c r="T134" s="14" t="inlineStr"/>
+          <t>zaubacorp.com</t>
+        </is>
+      </c>
+      <c r="T134" s="13" t="inlineStr">
+        <is>
+          <t>mahesh.kasani@gmail.com</t>
+        </is>
+      </c>
       <c r="U134" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -11647,16 +11655,16 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Fresco Drone Services LLP</t>
+          <t>Airserve Initiatives</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
         <is>
-          <t>zaubacorp.com</t>
+          <t>airserve.io</t>
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E135" s="18" t="inlineStr">
         <is>
@@ -11665,66 +11673,70 @@
       </c>
       <c r="F135" s="18" t="inlineStr">
         <is>
-          <t>APAC(India)</t>
+          <t>NA(United States); APAC(India)</t>
         </is>
       </c>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; United States</t>
         </is>
       </c>
       <c r="H135" s="18" t="inlineStr">
         <is>
-          <t>Joint Venture</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I135" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J135" s="18" t="inlineStr">
         <is>
-          <t>Commercial drone field work; industrial aerial imaging; site inspection workflows</t>
+          <t>Aerial surveys; Infrastructure inspection; Drone analytics</t>
         </is>
       </c>
       <c r="K135" s="18" t="inlineStr">
         <is>
-          <t>Local regional service delivery for infrastructure, layout surveying, and utilities across Telangana corridors</t>
+          <t>UAV data acquisition and analytics for construction, infrastructure, and agriculture sectors</t>
         </is>
       </c>
       <c r="L135" s="18" t="inlineStr">
         <is>
-          <t>High-definition orthomosaic mapping arrays, topography point cloud outputs, and localized agricultural spraying</t>
+          <t>AST-001 fixed-wing energy meter reading drones, medical payload delivery systems, proprietary mapping analytics software</t>
         </is>
       </c>
       <c r="M135" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N135" s="18" t="inlineStr"/>
       <c r="O135" s="18" t="inlineStr"/>
       <c r="P135" s="17" t="inlineStr">
         <is>
-          <t>mahesh.kasani@gmail.com</t>
+          <t>info@airserve.io</t>
         </is>
       </c>
       <c r="Q135" s="18" t="inlineStr"/>
-      <c r="R135" s="18" t="inlineStr"/>
+      <c r="R135" s="18" t="inlineStr">
+        <is>
+          <t>+91 40-23000123</t>
+        </is>
+      </c>
       <c r="S135" s="17" t="inlineStr">
         <is>
-          <t>zaubacorp.com</t>
+          <t>airserve.io</t>
         </is>
       </c>
       <c r="T135" s="17" t="inlineStr">
         <is>
-          <t>mahesh.kasani@gmail.com</t>
+          <t>info@airserve.io</t>
         </is>
       </c>
       <c r="U135" s="15" t="inlineStr">
         <is>
-          <t>+91 / IN</t>
+          <t>+91 / IN; +1 / US</t>
         </is>
       </c>
     </row>
@@ -11734,16 +11746,16 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>Airserve Initiatives</t>
+          <t>Pavaman Aviation</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>airserve.io</t>
+          <t>pavaman.in</t>
         </is>
       </c>
       <c r="D136" s="11" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
@@ -11752,12 +11764,12 @@
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
-          <t>NA(United States); APAC(India)</t>
+          <t>APAC(India)</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>India; United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr">
@@ -11772,17 +11784,17 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>Aerial surveys; Infrastructure inspection; Drone analytics</t>
+          <t>Remote pilot training; Precision agricultural spraying; Mining surveillance</t>
         </is>
       </c>
       <c r="K136" s="14" t="inlineStr">
         <is>
-          <t>UAV data acquisition and analytics for construction, infrastructure, and agriculture sectors</t>
+          <t>DGCA-approved professional drone pilot training and smart crop protection management</t>
         </is>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>AST-001 fixed-wing energy meter reading drones, medical payload delivery systems, proprietary mapping analytics software</t>
+          <t>Teja-S agriculture drone platform, long-endurance fixed-wing surveillance drones, asset lease operational schemes</t>
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr">
@@ -11794,28 +11806,28 @@
       <c r="O136" s="14" t="inlineStr"/>
       <c r="P136" s="13" t="inlineStr">
         <is>
-          <t>info@airserve.io</t>
+          <t>info.aviation@pavaman.in</t>
         </is>
       </c>
       <c r="Q136" s="14" t="inlineStr"/>
       <c r="R136" s="14" t="inlineStr">
         <is>
-          <t>+91 40-23000123</t>
+          <t>+91 8977861466</t>
         </is>
       </c>
       <c r="S136" s="13" t="inlineStr">
         <is>
-          <t>airserve.io</t>
+          <t>pavaman.in</t>
         </is>
       </c>
       <c r="T136" s="13" t="inlineStr">
         <is>
-          <t>info@airserve.io</t>
+          <t>info.aviation@pavaman.in</t>
         </is>
       </c>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>+91 / IN; +1 / US</t>
+          <t>+91 / IN</t>
         </is>
       </c>
     </row>
@@ -11825,16 +11837,16 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>Pavaman Aviation</t>
+          <t>Deccan Survey Solutions</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
         <is>
-          <t>pavaman.in</t>
+          <t>deccansurveysolutions.com</t>
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E137" s="18" t="inlineStr">
         <is>
@@ -11863,45 +11875,45 @@
       </c>
       <c r="J137" s="18" t="inlineStr">
         <is>
-          <t>Remote pilot training; Precision agricultural spraying; Mining surveillance</t>
+          <t>Drone surveying; Contour mapping; GIS data mapping</t>
         </is>
       </c>
       <c r="K137" s="18" t="inlineStr">
         <is>
-          <t>DGCA-approved professional drone pilot training and smart crop protection management</t>
+          <t>High-accuracy land surveying, layout layouts, and aerial drone photogrammetry data compilation for engineering projects</t>
         </is>
       </c>
       <c r="L137" s="18" t="inlineStr">
         <is>
-          <t>Teja-S agriculture drone platform, long-endurance fixed-wing surveillance drones, asset lease operational schemes</t>
+          <t>UAV aerial mapping arrays, differential GPS positioning tools, CAD and GIS file engineering systems</t>
         </is>
       </c>
       <c r="M137" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N137" s="18" t="inlineStr"/>
       <c r="O137" s="18" t="inlineStr"/>
       <c r="P137" s="17" t="inlineStr">
         <is>
-          <t>info.aviation@pavaman.in</t>
+          <t>deccan@deccansurveysolutions.com</t>
         </is>
       </c>
       <c r="Q137" s="18" t="inlineStr"/>
       <c r="R137" s="18" t="inlineStr">
         <is>
-          <t>+91 8977861466</t>
+          <t>+91 9700969638</t>
         </is>
       </c>
       <c r="S137" s="17" t="inlineStr">
         <is>
-          <t>pavaman.in</t>
+          <t>deccansurveysolutions.com</t>
         </is>
       </c>
       <c r="T137" s="17" t="inlineStr">
         <is>
-          <t>info.aviation@pavaman.in</t>
+          <t>deccan@deccansurveysolutions.com</t>
         </is>
       </c>
       <c r="U137" s="15" t="inlineStr">
@@ -11910,22 +11922,22 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="46.5" customHeight="1">
+    <row r="138" ht="33" customHeight="1">
       <c r="A138" s="11" t="n">
         <v>133</v>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>Deccan Survey Solutions</t>
+          <t>Hornbill Technologies Private Limited</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>deccansurveysolutions.com</t>
+          <t>https://hornbill.technology</t>
         </is>
       </c>
       <c r="D138" s="11" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
@@ -11934,12 +11946,12 @@
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
-          <t>APAC(India)</t>
+          <t>EU(Germany); APAC(India, Australia)</t>
         </is>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; Australia; Germany</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
@@ -11954,69 +11966,65 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>Drone surveying; Contour mapping; GIS data mapping</t>
+          <t>UAV inspection analytics software; Thermographic inspection services</t>
         </is>
       </c>
       <c r="K138" s="14" t="inlineStr">
         <is>
-          <t>High-accuracy land surveying, layout layouts, and aerial drone photogrammetry data compilation for engineering projects</t>
+          <t>AI-powered data intelligence for energy infrastructure</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>UAV aerial mapping arrays, differential GPS positioning tools, CAD and GIS file engineering systems</t>
+          <t>SolarWise, WindWise, and GridWise portals</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N138" s="14" t="inlineStr"/>
       <c r="O138" s="14" t="inlineStr"/>
-      <c r="P138" s="13" t="inlineStr">
-        <is>
-          <t>deccan@deccansurveysolutions.com</t>
-        </is>
-      </c>
+      <c r="P138" s="14" t="inlineStr"/>
       <c r="Q138" s="14" t="inlineStr"/>
       <c r="R138" s="14" t="inlineStr">
         <is>
-          <t>+91 9700969638</t>
+          <t>+91 97425 68404</t>
         </is>
       </c>
       <c r="S138" s="13" t="inlineStr">
         <is>
-          <t>deccansurveysolutions.com</t>
+          <t>https://hornbill.technology</t>
         </is>
       </c>
       <c r="T138" s="13" t="inlineStr">
         <is>
-          <t>deccan@deccansurveysolutions.com</t>
+          <t>contact@hornbilldrones.com</t>
         </is>
       </c>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>+91 / IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="33" customHeight="1">
+          <t>+91 / IN; +61 / AU; +49 / DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="46.5" customHeight="1">
       <c r="A139" s="15" t="n">
         <v>134</v>
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Hornbill Technologies Private Limited</t>
+          <t>Thanos Technologies Private Limited</t>
         </is>
       </c>
       <c r="C139" s="17" t="inlineStr">
         <is>
-          <t>https://hornbill.technology</t>
+          <t>http://www.thanos.in</t>
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E139" s="18" t="inlineStr">
         <is>
@@ -12025,12 +12033,12 @@
       </c>
       <c r="F139" s="18" t="inlineStr">
         <is>
-          <t>EU(Germany); APAC(India, Australia)</t>
+          <t>APAC(India)</t>
         </is>
       </c>
       <c r="G139" s="18" t="inlineStr">
         <is>
-          <t>India; Australia; Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H139" s="18" t="inlineStr">
@@ -12045,17 +12053,17 @@
       </c>
       <c r="J139" s="18" t="inlineStr">
         <is>
-          <t>UAV inspection analytics software; Thermographic inspection services</t>
+          <t>Spraying-as-a-service; Power line stringing solutions; Aerial automation workflows</t>
         </is>
       </c>
       <c r="K139" s="18" t="inlineStr">
         <is>
-          <t>AI-powered data intelligence for energy infrastructure</t>
+          <t>Autonomous payload delivery and aerial utility automation</t>
         </is>
       </c>
       <c r="L139" s="18" t="inlineStr">
         <is>
-          <t>SolarWise, WindWise, and GridWise portals</t>
+          <t>SYENA-H10i agricultural drone, utility stringing payloads</t>
         </is>
       </c>
       <c r="M139" s="15" t="inlineStr">
@@ -12069,41 +12077,41 @@
       <c r="Q139" s="18" t="inlineStr"/>
       <c r="R139" s="18" t="inlineStr">
         <is>
-          <t>+91 97425 68404</t>
+          <t>+91 91543 70050</t>
         </is>
       </c>
       <c r="S139" s="17" t="inlineStr">
         <is>
-          <t>https://hornbill.technology</t>
+          <t>http://www.thanos.in</t>
         </is>
       </c>
       <c r="T139" s="17" t="inlineStr">
         <is>
-          <t>contact@hornbilldrones.com</t>
+          <t>info@thanos.in</t>
         </is>
       </c>
       <c r="U139" s="15" t="inlineStr">
         <is>
-          <t>+91 / IN; +61 / AU; +49 / DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="46.5" customHeight="1">
+          <t>+91 / IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="33" customHeight="1">
       <c r="A140" s="11" t="n">
         <v>135</v>
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>Thanos Technologies Private Limited</t>
+          <t>Aerial Technologies Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>http://www.thanos.in</t>
+          <t>aerialtechnologie.com</t>
         </is>
       </c>
       <c r="D140" s="11" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
@@ -12132,17 +12140,17 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>Spraying-as-a-service; Power line stringing solutions; Aerial automation workflows</t>
+          <t>Drone survey and mapping; agriculture drone spraying</t>
         </is>
       </c>
       <c r="K140" s="14" t="inlineStr">
         <is>
-          <t>Autonomous payload delivery and aerial utility automation</t>
+          <t>UAV land surveying and agricultural drone services</t>
         </is>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
-          <t>SYENA-H10i agricultural drone, utility stringing payloads</t>
+          <t>Orthomosaic mapping, drone land surveying, pesticide spraying</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr">
@@ -12154,21 +12162,13 @@
       <c r="O140" s="14" t="inlineStr"/>
       <c r="P140" s="14" t="inlineStr"/>
       <c r="Q140" s="14" t="inlineStr"/>
-      <c r="R140" s="14" t="inlineStr">
-        <is>
-          <t>+91 91543 70050</t>
-        </is>
-      </c>
+      <c r="R140" s="14" t="inlineStr"/>
       <c r="S140" s="13" t="inlineStr">
         <is>
-          <t>http://www.thanos.in</t>
-        </is>
-      </c>
-      <c r="T140" s="13" t="inlineStr">
-        <is>
-          <t>info@thanos.in</t>
-        </is>
-      </c>
+          <t>aerialtechnologie.com</t>
+        </is>
+      </c>
+      <c r="T140" s="14" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12181,16 +12181,16 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Aerial Technologies Pvt. Ltd.</t>
+          <t>Polygon Geospatial</t>
         </is>
       </c>
       <c r="C141" s="17" t="inlineStr">
         <is>
-          <t>aerialtechnologie.com</t>
+          <t>polygongeo.com</t>
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="J141" s="18" t="inlineStr">
         <is>
-          <t>Drone survey and mapping; agriculture drone spraying</t>
+          <t>Drone land record management; spatial layout verification services</t>
         </is>
       </c>
       <c r="K141" s="18" t="inlineStr">
         <is>
-          <t>UAV land surveying and agricultural drone services</t>
+          <t>Real estate layouts and spatial feature extraction using drone surveys</t>
         </is>
       </c>
       <c r="L141" s="18" t="inlineStr">
         <is>
-          <t>Orthomosaic mapping, drone land surveying, pesticide spraying</t>
+          <t>Drone land acquisition surveys, layout photogrammetry</t>
         </is>
       </c>
       <c r="M141" s="15" t="inlineStr">
@@ -12244,7 +12244,7 @@
       <c r="R141" s="18" t="inlineStr"/>
       <c r="S141" s="17" t="inlineStr">
         <is>
-          <t>aerialtechnologie.com</t>
+          <t>polygongeo.com</t>
         </is>
       </c>
       <c r="T141" s="18" t="inlineStr"/>
@@ -12260,16 +12260,16 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>Polygon Geospatial</t>
+          <t>Navi Geospatial Services</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>polygongeo.com</t>
+          <t>navigeospatial.com</t>
         </is>
       </c>
       <c r="D142" s="11" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
@@ -12298,17 +12298,17 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>Drone land record management; spatial layout verification services</t>
+          <t>Photogrammetry mapping; LiDAR data processing services</t>
         </is>
       </c>
       <c r="K142" s="14" t="inlineStr">
         <is>
-          <t>Real estate layouts and spatial feature extraction using drone surveys</t>
+          <t>LiDAR and digital orthophotography mapping</t>
         </is>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>Drone land acquisition surveys, layout photogrammetry</t>
+          <t>Mobile and aerial LiDAR processing, aerial triangulation</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr">
@@ -12323,7 +12323,7 @@
       <c r="R142" s="14" t="inlineStr"/>
       <c r="S142" s="13" t="inlineStr">
         <is>
-          <t>polygongeo.com</t>
+          <t>navigeospatial.com</t>
         </is>
       </c>
       <c r="T142" s="14" t="inlineStr"/>
@@ -12339,16 +12339,16 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Navi Geospatial Services</t>
+          <t>RSI Softech India Pvt Ltd</t>
         </is>
       </c>
       <c r="C143" s="17" t="inlineStr">
         <is>
-          <t>navigeospatial.com</t>
+          <t>rsisoftech.com</t>
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>2021</v>
+        <v>2000</v>
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="J143" s="18" t="inlineStr">
         <is>
-          <t>Photogrammetry mapping; LiDAR data processing services</t>
+          <t>City drone mapping; utility geospatial surveys</t>
         </is>
       </c>
       <c r="K143" s="18" t="inlineStr">
         <is>
-          <t>LiDAR and digital orthophotography mapping</t>
+          <t>Turnkey enterprise geospatial solutions and field mapping integrations</t>
         </is>
       </c>
       <c r="L143" s="18" t="inlineStr">
         <is>
-          <t>Mobile and aerial LiDAR processing, aerial triangulation</t>
+          <t>Drone city mapping, DGPS surveys, utility mapping</t>
         </is>
       </c>
       <c r="M143" s="15" t="inlineStr">
@@ -12402,7 +12402,7 @@
       <c r="R143" s="18" t="inlineStr"/>
       <c r="S143" s="17" t="inlineStr">
         <is>
-          <t>navigeospatial.com</t>
+          <t>rsisoftech.com</t>
         </is>
       </c>
       <c r="T143" s="18" t="inlineStr"/>
@@ -12418,16 +12418,16 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>RSI Softech India Pvt Ltd</t>
+          <t>Jeevan Drones and Energy Tech Pvt Ltd</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>rsisoftech.com</t>
+          <t>jdetechnologies.com</t>
         </is>
       </c>
       <c r="D144" s="11" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
@@ -12451,22 +12451,22 @@
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>City drone mapping; utility geospatial surveys</t>
+          <t>Agricultural drone services; crop surveillance and mapping services</t>
         </is>
       </c>
       <c r="K144" s="14" t="inlineStr">
         <is>
-          <t>Turnkey enterprise geospatial solutions and field mapping integrations</t>
+          <t>Smart farming solutions and surveillance data capture</t>
         </is>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>Drone city mapping, DGPS surveys, utility mapping</t>
+          <t>Type-certified agriculture drones, multispectral crop health analysis</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr">
@@ -12481,7 +12481,7 @@
       <c r="R144" s="14" t="inlineStr"/>
       <c r="S144" s="13" t="inlineStr">
         <is>
-          <t>rsisoftech.com</t>
+          <t>jdetechnologies.com</t>
         </is>
       </c>
       <c r="T144" s="14" t="inlineStr"/>
@@ -12491,22 +12491,22 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="33" customHeight="1">
+    <row r="145" ht="46.5" customHeight="1">
       <c r="A145" s="15" t="n">
         <v>140</v>
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Jeevan Drones and Energy Tech Pvt Ltd</t>
+          <t>OQLO AI</t>
         </is>
       </c>
       <c r="C145" s="17" t="inlineStr">
         <is>
-          <t>jdetechnologies.com</t>
+          <t>oqlo.ai</t>
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
@@ -12535,17 +12535,17 @@
       </c>
       <c r="J145" s="18" t="inlineStr">
         <is>
-          <t>Agricultural drone services; crop surveillance and mapping services</t>
+          <t>Topographic mapping; Volumetric analysis; 3D digital twin modeling; Construction progress tracking</t>
         </is>
       </c>
       <c r="K145" s="18" t="inlineStr">
         <is>
-          <t>Smart farming solutions and surveillance data capture</t>
+          <t>AI-augmented aerial surveying and autonomous site diagnostics for high-precision engineering projects</t>
         </is>
       </c>
       <c r="L145" s="18" t="inlineStr">
         <is>
-          <t>Type-certified agriculture drones, multispectral crop health analysis</t>
+          <t>RGB survey drones; Mobile LiDAR scanners; 3D visualization cloud platform; AI computer vision engines</t>
         </is>
       </c>
       <c r="M145" s="15" t="inlineStr">
@@ -12553,17 +12553,37 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N145" s="18" t="inlineStr"/>
-      <c r="O145" s="18" t="inlineStr"/>
-      <c r="P145" s="18" t="inlineStr"/>
+      <c r="N145" s="18" t="inlineStr">
+        <is>
+          <t>Sivaji Koppisetti</t>
+        </is>
+      </c>
+      <c r="O145" s="18" t="inlineStr">
+        <is>
+          <t>AI Product Manager</t>
+        </is>
+      </c>
+      <c r="P145" s="17" t="inlineStr">
+        <is>
+          <t>sales@oqlo.ai</t>
+        </is>
+      </c>
       <c r="Q145" s="18" t="inlineStr"/>
-      <c r="R145" s="18" t="inlineStr"/>
+      <c r="R145" s="18" t="inlineStr">
+        <is>
+          <t>+91 79955 54904</t>
+        </is>
+      </c>
       <c r="S145" s="17" t="inlineStr">
         <is>
-          <t>jdetechnologies.com</t>
-        </is>
-      </c>
-      <c r="T145" s="18" t="inlineStr"/>
+          <t>oqlo.ai</t>
+        </is>
+      </c>
+      <c r="T145" s="17" t="inlineStr">
+        <is>
+          <t>sales@oqlo.ai</t>
+        </is>
+      </c>
       <c r="U145" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12576,16 +12596,16 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>OQLO AI</t>
+          <t>Akin Analytics Solutions Private Limited</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>oqlo.ai</t>
+          <t>https://www.akinanalytics.com</t>
         </is>
       </c>
       <c r="D146" s="11" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
@@ -12614,17 +12634,17 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>Topographic mapping; Volumetric analysis; 3D digital twin modeling; Construction progress tracking</t>
+          <t>AI drone analytics; Aquaculture feed distribution; Plantations terrain-following mapping; Digital twin modeling</t>
         </is>
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>AI-augmented aerial surveying and autonomous site diagnostics for high-precision engineering projects</t>
+          <t>DeepTech and defense-grade multi-payload aerial solutions tailored for challenging and sloping landscapes</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>RGB survey drones; Mobile LiDAR scanners; 3D visualization cloud platform; AI computer vision engines</t>
+          <t>NIKA2 Kisan Medium Drone; AI-Augmented Analytics Platform; Quick-change payload mechanisms</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr">
@@ -12634,33 +12654,33 @@
       </c>
       <c r="N146" s="14" t="inlineStr">
         <is>
-          <t>Sivaji Koppisetti</t>
+          <t>Janaki Pulaparthi</t>
         </is>
       </c>
       <c r="O146" s="14" t="inlineStr">
         <is>
-          <t>AI Product Manager</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="P146" s="13" t="inlineStr">
         <is>
-          <t>sales@oqlo.ai</t>
+          <t>info@akinanalytics.com</t>
         </is>
       </c>
       <c r="Q146" s="14" t="inlineStr"/>
       <c r="R146" s="14" t="inlineStr">
         <is>
-          <t>+91 79955 54904</t>
+          <t>+91 73372 92216</t>
         </is>
       </c>
       <c r="S146" s="13" t="inlineStr">
         <is>
-          <t>oqlo.ai</t>
+          <t>https://www.akinanalytics.com</t>
         </is>
       </c>
       <c r="T146" s="13" t="inlineStr">
         <is>
-          <t>sales@oqlo.ai</t>
+          <t>info@akinanalytics.com</t>
         </is>
       </c>
       <c r="U146" s="11" t="inlineStr">
@@ -12675,16 +12695,16 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Akin Analytics Solutions Private Limited</t>
+          <t>Soaron Aerospace Innovations Private Limited</t>
         </is>
       </c>
       <c r="C147" s="17" t="inlineStr">
         <is>
-          <t>https://www.akinanalytics.com</t>
+          <t>http://www.soaron.co</t>
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
@@ -12708,22 +12728,22 @@
       </c>
       <c r="I147" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J147" s="18" t="inlineStr">
         <is>
-          <t>AI drone analytics; Aquaculture feed distribution; Plantations terrain-following mapping; Digital twin modeling</t>
+          <t>Aerial coloring operations; High-rise facade maintenance; Structural surface coating; Construction automation</t>
         </is>
       </c>
       <c r="K147" s="18" t="inlineStr">
         <is>
-          <t>DeepTech and defense-grade multi-payload aerial solutions tailored for challenging and sloping landscapes</t>
+          <t>Automating hazardous and labor-intensive activities at height using heavy industrial drone platforms</t>
         </is>
       </c>
       <c r="L147" s="18" t="inlineStr">
         <is>
-          <t>NIKA2 Kisan Medium Drone; AI-Augmented Analytics Platform; Quick-change payload mechanisms</t>
+          <t>Colorown autonomous painting system; Soaron FlyFree mobile ecosystem; Custom multirotor spray attachments</t>
         </is>
       </c>
       <c r="M147" s="15" t="inlineStr">
@@ -12733,33 +12753,29 @@
       </c>
       <c r="N147" s="18" t="inlineStr">
         <is>
-          <t>Janaki Pulaparthi</t>
+          <t>Syed Shariq Ahmed</t>
         </is>
       </c>
       <c r="O147" s="18" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Co-founder &amp; CEO</t>
         </is>
       </c>
       <c r="P147" s="17" t="inlineStr">
         <is>
-          <t>info@akinanalytics.com</t>
+          <t>info@soaron.co</t>
         </is>
       </c>
       <c r="Q147" s="18" t="inlineStr"/>
-      <c r="R147" s="18" t="inlineStr">
-        <is>
-          <t>+91 73372 92216</t>
-        </is>
-      </c>
+      <c r="R147" s="18" t="inlineStr"/>
       <c r="S147" s="17" t="inlineStr">
         <is>
-          <t>https://www.akinanalytics.com</t>
+          <t>http://www.soaron.co</t>
         </is>
       </c>
       <c r="T147" s="17" t="inlineStr">
         <is>
-          <t>info@akinanalytics.com</t>
+          <t>info@soaron.co</t>
         </is>
       </c>
       <c r="U147" s="15" t="inlineStr">
@@ -12774,16 +12790,16 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>Soaron Aerospace Innovations Private Limited</t>
+          <t>DigiTwin Mapping LLP</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>http://www.soaron.co</t>
+          <t>digitwinmaps.com</t>
         </is>
       </c>
       <c r="D148" s="11" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
@@ -12802,7 +12818,7 @@
       </c>
       <c r="H148" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Joint Venture</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
@@ -12812,73 +12828,57 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>Aerial coloring operations; High-rise facade maintenance; Structural surface coating; Construction automation</t>
+          <t>Photogrammetric layout generation; GIS/CAD drafting; UAV asset scanning; Aerial data analysis</t>
         </is>
       </c>
       <c r="K148" s="14" t="inlineStr">
         <is>
-          <t>Automating hazardous and labor-intensive activities at height using heavy industrial drone platforms</t>
+          <t>High-accuracy digital twin environment replicas and spatial models optimized for real estate and construction asset management</t>
         </is>
       </c>
       <c r="L148" s="14" t="inlineStr">
         <is>
-          <t>Colorown autonomous painting system; Soaron FlyFree mobile ecosystem; Custom multirotor spray attachments</t>
+          <t>UAV LiDAR sensors; Aerial data capture kits; Photogrammetry workstations</t>
         </is>
       </c>
       <c r="M148" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N148" s="14" t="inlineStr">
-        <is>
-          <t>Syed Shariq Ahmed</t>
-        </is>
-      </c>
-      <c r="O148" s="14" t="inlineStr">
-        <is>
-          <t>Co-founder &amp; CEO</t>
-        </is>
-      </c>
-      <c r="P148" s="13" t="inlineStr">
-        <is>
-          <t>info@soaron.co</t>
-        </is>
-      </c>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N148" s="14" t="inlineStr"/>
+      <c r="O148" s="14" t="inlineStr"/>
+      <c r="P148" s="14" t="inlineStr"/>
       <c r="Q148" s="14" t="inlineStr"/>
       <c r="R148" s="14" t="inlineStr"/>
       <c r="S148" s="13" t="inlineStr">
         <is>
-          <t>http://www.soaron.co</t>
-        </is>
-      </c>
-      <c r="T148" s="13" t="inlineStr">
-        <is>
-          <t>info@soaron.co</t>
-        </is>
-      </c>
+          <t>digitwinmaps.com</t>
+        </is>
+      </c>
+      <c r="T148" s="14" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="46.5" customHeight="1">
+    <row r="149" ht="60" customHeight="1">
       <c r="A149" s="15" t="n">
         <v>144</v>
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>DigiTwin Mapping LLP</t>
+          <t>drony.in</t>
         </is>
       </c>
       <c r="C149" s="17" t="inlineStr">
         <is>
-          <t>digitwinmaps.com</t>
+          <t>drony.in</t>
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="H149" s="18" t="inlineStr">
         <is>
-          <t>Joint Venture</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I149" s="15" t="inlineStr">
@@ -12907,32 +12907,36 @@
       </c>
       <c r="J149" s="18" t="inlineStr">
         <is>
-          <t>Photogrammetric layout generation; GIS/CAD drafting; UAV asset scanning; Aerial data analysis</t>
+          <t>Aerial industrial inspection; 3D topographical reconstruction; Aerial videography datasets; Corporate mapping field-work</t>
         </is>
       </c>
       <c r="K149" s="18" t="inlineStr">
         <is>
-          <t>High-accuracy digital twin environment replicas and spatial models optimized for real estate and construction asset management</t>
+          <t>Rapid turnaround drone mapping and professional asset visibility for local infrastructure projects</t>
         </is>
       </c>
       <c r="L149" s="18" t="inlineStr">
         <is>
-          <t>UAV LiDAR sensors; Aerial data capture kits; Photogrammetry workstations</t>
+          <t>DGCA-certified quadcopters; High-resolution aerial optical payloads; 3D surface modeling engines</t>
         </is>
       </c>
       <c r="M149" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N149" s="18" t="inlineStr"/>
       <c r="O149" s="18" t="inlineStr"/>
       <c r="P149" s="18" t="inlineStr"/>
       <c r="Q149" s="18" t="inlineStr"/>
-      <c r="R149" s="18" t="inlineStr"/>
+      <c r="R149" s="18" t="inlineStr">
+        <is>
+          <t>+91 89199 40257</t>
+        </is>
+      </c>
       <c r="S149" s="17" t="inlineStr">
         <is>
-          <t>digitwinmaps.com</t>
+          <t>drony.in</t>
         </is>
       </c>
       <c r="T149" s="18" t="inlineStr"/>
@@ -12942,22 +12946,22 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="60" customHeight="1">
+    <row r="150" ht="46.5" customHeight="1">
       <c r="A150" s="11" t="n">
         <v>145</v>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>drony.in</t>
+          <t>Drogo Aerospace Private Limited</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>drony.in</t>
+          <t>drogoaerospace.com</t>
         </is>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
@@ -12976,27 +12980,27 @@
       </c>
       <c r="H150" s="14" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>250-500</t>
         </is>
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>Aerial industrial inspection; 3D topographical reconstruction; Aerial videography datasets; Corporate mapping field-work</t>
+          <t>Drone surveillance; Volumetric mine analysis; Agriculture drone spraying</t>
         </is>
       </c>
       <c r="K150" s="14" t="inlineStr">
         <is>
-          <t>Rapid turnaround drone mapping and professional asset visibility for local infrastructure projects</t>
+          <t>Turnkey commercial aerial mapping and high-endurance military defense intelligence operations</t>
         </is>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>DGCA-certified quadcopters; High-resolution aerial optical payloads; 3D surface modeling engines</t>
+          <t>JK250 surveillance drone, Nova Plus geospatial data analytics software</t>
         </is>
       </c>
       <c r="M150" s="11" t="inlineStr">
@@ -13004,18 +13008,22 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N150" s="14" t="inlineStr"/>
-      <c r="O150" s="14" t="inlineStr"/>
+      <c r="N150" s="14" t="inlineStr">
+        <is>
+          <t>Yashwanth Bonthu</t>
+        </is>
+      </c>
+      <c r="O150" s="14" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="P150" s="14" t="inlineStr"/>
       <c r="Q150" s="14" t="inlineStr"/>
-      <c r="R150" s="14" t="inlineStr">
-        <is>
-          <t>+91 89199 40257</t>
-        </is>
-      </c>
+      <c r="R150" s="14" t="inlineStr"/>
       <c r="S150" s="13" t="inlineStr">
         <is>
-          <t>drony.in</t>
+          <t>drogoaerospace.com</t>
         </is>
       </c>
       <c r="T150" s="14" t="inlineStr"/>
@@ -13031,16 +13039,16 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Drogo Aerospace Private Limited</t>
+          <t>Dharani Geospatial Technologies LLP</t>
         </is>
       </c>
       <c r="C151" s="17" t="inlineStr">
         <is>
-          <t>drogoaerospace.com</t>
+          <t>dharanigeospatialtechnologies.com</t>
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E151" s="18" t="inlineStr">
         <is>
@@ -13064,22 +13072,22 @@
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
-          <t>250-500</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J151" s="18" t="inlineStr">
         <is>
-          <t>Drone surveillance; Volumetric mine analysis; Agriculture drone spraying</t>
+          <t>Aerial LiDAR processing; UAV topography surveys; Orthophotography data capture</t>
         </is>
       </c>
       <c r="K151" s="18" t="inlineStr">
         <is>
-          <t>Turnkey commercial aerial mapping and high-endurance military defense intelligence operations</t>
+          <t>High-accuracy topographic mapping, contouring, and 3D building information models via drone inputs</t>
         </is>
       </c>
       <c r="L151" s="18" t="inlineStr">
         <is>
-          <t>JK250 surveillance drone, Nova Plus geospatial data analytics software</t>
+          <t>UAV photogrammetric mapping workflows, LiDAR terrain feature extraction software</t>
         </is>
       </c>
       <c r="M151" s="15" t="inlineStr">
@@ -13089,20 +13097,24 @@
       </c>
       <c r="N151" s="18" t="inlineStr">
         <is>
-          <t>Yashwanth Bonthu</t>
+          <t>Naveen Choudam</t>
         </is>
       </c>
       <c r="O151" s="18" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Founder and Owner</t>
         </is>
       </c>
       <c r="P151" s="18" t="inlineStr"/>
       <c r="Q151" s="18" t="inlineStr"/>
-      <c r="R151" s="18" t="inlineStr"/>
+      <c r="R151" s="18" t="inlineStr">
+        <is>
+          <t>+91 9542180946</t>
+        </is>
+      </c>
       <c r="S151" s="17" t="inlineStr">
         <is>
-          <t>drogoaerospace.com</t>
+          <t>dharanigeospatialtechnologies.com</t>
         </is>
       </c>
       <c r="T151" s="18" t="inlineStr"/>
@@ -13118,12 +13130,12 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>Dharani Geospatial Technologies LLP</t>
-        </is>
-      </c>
-      <c r="C152" s="13" t="inlineStr">
-        <is>
-          <t>dharanigeospatialtechnologies.com</t>
+          <t>Vayu Drone Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>vayu-drone-technologies-pvt-ltd</t>
         </is>
       </c>
       <c r="D152" s="11" t="n">
@@ -13131,7 +13143,7 @@
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Secunderabad, India</t>
         </is>
       </c>
       <c r="F152" s="14" t="inlineStr">
@@ -13156,73 +13168,69 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>Aerial LiDAR processing; UAV topography surveys; Orthophotography data capture</t>
+          <t>Custom multi-sensor aerial payloads; GIS analytics datasets</t>
         </is>
       </c>
       <c r="K152" s="14" t="inlineStr">
         <is>
-          <t>High-accuracy topographic mapping, contouring, and 3D building information models via drone inputs</t>
+          <t>Custom rotary and fixed-wing fabrications for precision surveillance and crop monitoring workflows</t>
         </is>
       </c>
       <c r="L152" s="14" t="inlineStr">
         <is>
-          <t>UAV photogrammetric mapping workflows, LiDAR terrain feature extraction software</t>
+          <t>Multispectral and thermal sensor payloads, Pesticide drone spraying systems, Approved DGCA flight certification programs</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N152" s="14" t="inlineStr">
-        <is>
-          <t>Naveen Choudam</t>
-        </is>
-      </c>
-      <c r="O152" s="14" t="inlineStr">
-        <is>
-          <t>Founder and Owner</t>
-        </is>
-      </c>
-      <c r="P152" s="14" t="inlineStr"/>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N152" s="14" t="inlineStr"/>
+      <c r="O152" s="14" t="inlineStr"/>
+      <c r="P152" s="13" t="inlineStr">
+        <is>
+          <t>vayudronetechnologies@gmail.com</t>
+        </is>
+      </c>
       <c r="Q152" s="14" t="inlineStr"/>
-      <c r="R152" s="14" t="inlineStr">
-        <is>
-          <t>+91 9542180946</t>
-        </is>
-      </c>
-      <c r="S152" s="13" t="inlineStr">
-        <is>
-          <t>dharanigeospatialtechnologies.com</t>
-        </is>
-      </c>
-      <c r="T152" s="14" t="inlineStr"/>
+      <c r="R152" s="14" t="inlineStr"/>
+      <c r="S152" s="14" t="inlineStr">
+        <is>
+          <t>vayu-drone-technologies-pvt-ltd</t>
+        </is>
+      </c>
+      <c r="T152" s="13" t="inlineStr">
+        <is>
+          <t>vayudronetechnologies@gmail.com</t>
+        </is>
+      </c>
       <c r="U152" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="46.5" customHeight="1">
+    <row r="153" ht="33" customHeight="1">
       <c r="A153" s="15" t="n">
         <v>148</v>
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Vayu Drone Technologies Private Limited</t>
+          <t>TMS Agri Drone Services LLP</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>vayu-drone-technologies-pvt-ltd</t>
+          <t>tms-agri-drone-services-llp</t>
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
-          <t>Secunderabad, India</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="F153" s="18" t="inlineStr">
@@ -13242,22 +13250,22 @@
       </c>
       <c r="I153" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J153" s="18" t="inlineStr">
         <is>
-          <t>Custom multi-sensor aerial payloads; GIS analytics datasets</t>
+          <t>Agricultural crop spraying data sets; Farm management monitoring metrics</t>
         </is>
       </c>
       <c r="K153" s="18" t="inlineStr">
         <is>
-          <t>Custom rotary and fixed-wing fabrications for precision surveillance and crop monitoring workflows</t>
+          <t>Commercial agriculture spraying optimization and remote precision imagery capture</t>
         </is>
       </c>
       <c r="L153" s="18" t="inlineStr">
         <is>
-          <t>Multispectral and thermal sensor payloads, Pesticide drone spraying systems, Approved DGCA flight certification programs</t>
+          <t>Precision flight capture protocols, Agronomic vegetation health analytics solutions</t>
         </is>
       </c>
       <c r="M153" s="15" t="inlineStr">
@@ -13267,45 +13275,37 @@
       </c>
       <c r="N153" s="18" t="inlineStr"/>
       <c r="O153" s="18" t="inlineStr"/>
-      <c r="P153" s="17" t="inlineStr">
-        <is>
-          <t>vayudronetechnologies@gmail.com</t>
-        </is>
-      </c>
+      <c r="P153" s="18" t="inlineStr"/>
       <c r="Q153" s="18" t="inlineStr"/>
       <c r="R153" s="18" t="inlineStr"/>
       <c r="S153" s="18" t="inlineStr">
         <is>
-          <t>vayu-drone-technologies-pvt-ltd</t>
-        </is>
-      </c>
-      <c r="T153" s="17" t="inlineStr">
-        <is>
-          <t>vayudronetechnologies@gmail.com</t>
-        </is>
-      </c>
+          <t>tms-agri-drone-services-llp</t>
+        </is>
+      </c>
+      <c r="T153" s="18" t="inlineStr"/>
       <c r="U153" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="33" customHeight="1">
+    <row r="154" ht="46.5" customHeight="1">
       <c r="A154" s="11" t="n">
         <v>149</v>
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>TMS Agri Drone Services LLP</t>
-        </is>
-      </c>
-      <c r="C154" s="14" t="inlineStr">
-        <is>
-          <t>tms-agri-drone-services-llp</t>
+          <t>Exodrone Systems Private Limited</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="inlineStr">
+        <is>
+          <t>exosl.com</t>
         </is>
       </c>
       <c r="D154" s="11" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
@@ -13329,40 +13329,56 @@
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-25</t>
         </is>
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>Agricultural crop spraying data sets; Farm management monitoring metrics</t>
+          <t>Land topographic surveys; Composite unmanned aerial systems</t>
         </is>
       </c>
       <c r="K154" s="14" t="inlineStr">
         <is>
-          <t>Commercial agriculture spraying optimization and remote precision imagery capture</t>
+          <t>Indigenous custom airframe engineering and industrial drone site mapping</t>
         </is>
       </c>
       <c r="L154" s="14" t="inlineStr">
         <is>
-          <t>Precision flight capture protocols, Agronomic vegetation health analytics solutions</t>
+          <t>Fixed-wing survey systems, hybrid multi-copter platforms, and drone spraying technologies</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N154" s="14" t="inlineStr"/>
-      <c r="O154" s="14" t="inlineStr"/>
-      <c r="P154" s="14" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N154" s="14" t="inlineStr">
+        <is>
+          <t>Siddhartha Barabari</t>
+        </is>
+      </c>
+      <c r="O154" s="14" t="inlineStr">
+        <is>
+          <t>Founder and Engineer</t>
+        </is>
+      </c>
+      <c r="P154" s="13" t="inlineStr">
+        <is>
+          <t>filingezee@gmail.com</t>
+        </is>
+      </c>
       <c r="Q154" s="14" t="inlineStr"/>
       <c r="R154" s="14" t="inlineStr"/>
-      <c r="S154" s="14" t="inlineStr">
-        <is>
-          <t>tms-agri-drone-services-llp</t>
-        </is>
-      </c>
-      <c r="T154" s="14" t="inlineStr"/>
+      <c r="S154" s="13" t="inlineStr">
+        <is>
+          <t>exosl.com</t>
+        </is>
+      </c>
+      <c r="T154" s="13" t="inlineStr">
+        <is>
+          <t>filingezee@gmail.com</t>
+        </is>
+      </c>
       <c r="U154" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13375,16 +13391,16 @@
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>Exodrone Systems Private Limited</t>
+          <t>Geo Survey Solutions</t>
         </is>
       </c>
       <c r="C155" s="17" t="inlineStr">
         <is>
-          <t>exosl.com</t>
+          <t>geosurveysolution.in</t>
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
@@ -13408,54 +13424,50 @@
       </c>
       <c r="I155" s="15" t="inlineStr">
         <is>
-          <t>11-25</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J155" s="18" t="inlineStr">
         <is>
-          <t>Land topographic surveys; Composite unmanned aerial systems</t>
+          <t>DGPS field surveying; Topographical boundary and pipeline route mapping</t>
         </is>
       </c>
       <c r="K155" s="18" t="inlineStr">
         <is>
-          <t>Indigenous custom airframe engineering and industrial drone site mapping</t>
+          <t>Geodetic control networks, construction alignment mapping, and cadastral overlay analytics</t>
         </is>
       </c>
       <c r="L155" s="18" t="inlineStr">
         <is>
-          <t>Fixed-wing survey systems, hybrid multi-copter platforms, and drone spraying technologies</t>
+          <t>Differential Global Positioning System (DGPS) tracking, 3D Revit architectural modeling, and Trimble GPS data processing</t>
         </is>
       </c>
       <c r="M155" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N155" s="18" t="inlineStr">
-        <is>
-          <t>Siddhartha Barabari</t>
-        </is>
-      </c>
-      <c r="O155" s="18" t="inlineStr">
-        <is>
-          <t>Founder and Engineer</t>
-        </is>
-      </c>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N155" s="18" t="inlineStr"/>
+      <c r="O155" s="18" t="inlineStr"/>
       <c r="P155" s="17" t="inlineStr">
         <is>
-          <t>filingezee@gmail.com</t>
+          <t>info@geosurveysolution.in</t>
         </is>
       </c>
       <c r="Q155" s="18" t="inlineStr"/>
-      <c r="R155" s="18" t="inlineStr"/>
+      <c r="R155" s="18" t="inlineStr">
+        <is>
+          <t>+91 9966665892</t>
+        </is>
+      </c>
       <c r="S155" s="17" t="inlineStr">
         <is>
-          <t>exosl.com</t>
+          <t>geosurveysolution.in</t>
         </is>
       </c>
       <c r="T155" s="17" t="inlineStr">
         <is>
-          <t>filingezee@gmail.com</t>
+          <t>info@geosurveysolution.in</t>
         </is>
       </c>
       <c r="U155" s="15" t="inlineStr">
@@ -13470,16 +13482,16 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>Geo Survey Solutions</t>
+          <t>VisualHash Technologies</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>geosurveysolution.in</t>
+          <t>visualhash.tech</t>
         </is>
       </c>
       <c r="D156" s="11" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
@@ -13508,47 +13520,35 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>DGPS field surveying; Topographical boundary and pipeline route mapping</t>
+          <t>Real estate drone videography; Commercial aerial imaging</t>
         </is>
       </c>
       <c r="K156" s="14" t="inlineStr">
         <is>
-          <t>Geodetic control networks, construction alignment mapping, and cadastral overlay analytics</t>
+          <t>High-resolution architectural cinematography and commercial project tracking updates</t>
         </is>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>Differential Global Positioning System (DGPS) tracking, 3D Revit architectural modeling, and Trimble GPS data processing</t>
+          <t>Stabilized high-resolution cameras, autonomous intelligent flight planning setups, and digital media processing platforms</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N156" s="14" t="inlineStr"/>
       <c r="O156" s="14" t="inlineStr"/>
-      <c r="P156" s="13" t="inlineStr">
-        <is>
-          <t>info@geosurveysolution.in</t>
-        </is>
-      </c>
+      <c r="P156" s="14" t="inlineStr"/>
       <c r="Q156" s="14" t="inlineStr"/>
-      <c r="R156" s="14" t="inlineStr">
-        <is>
-          <t>+91 9966665892</t>
-        </is>
-      </c>
+      <c r="R156" s="14" t="inlineStr"/>
       <c r="S156" s="13" t="inlineStr">
         <is>
-          <t>geosurveysolution.in</t>
-        </is>
-      </c>
-      <c r="T156" s="13" t="inlineStr">
-        <is>
-          <t>info@geosurveysolution.in</t>
-        </is>
-      </c>
+          <t>visualhash.tech</t>
+        </is>
+      </c>
+      <c r="T156" s="14" t="inlineStr"/>
       <c r="U156" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13561,16 +13561,16 @@
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>VisualHash Technologies</t>
+          <t>GeoVista Technologies Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
         <is>
-          <t>visualhash.tech</t>
+          <t>geovista.in</t>
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
@@ -13594,40 +13594,56 @@
       </c>
       <c r="I157" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>201-500</t>
         </is>
       </c>
       <c r="J157" s="18" t="inlineStr">
         <is>
-          <t>Real estate drone videography; Commercial aerial imaging</t>
+          <t>Aerial photogrammetry services; UAV LiDAR scanning; topographic land surveying; GIS asset mapping</t>
         </is>
       </c>
       <c r="K157" s="18" t="inlineStr">
         <is>
-          <t>High-resolution architectural cinematography and commercial project tracking updates</t>
+          <t>Turnkey geospatial data acquisition, highway network mapping, and railway asset monitoring.</t>
         </is>
       </c>
       <c r="L157" s="18" t="inlineStr">
         <is>
-          <t>Stabilized high-resolution cameras, autonomous intelligent flight planning setups, and digital media processing platforms</t>
+          <t>UAV photogrammetry platforms, drone-mounted LiDAR arrays</t>
         </is>
       </c>
       <c r="M157" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N157" s="18" t="inlineStr"/>
-      <c r="O157" s="18" t="inlineStr"/>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N157" s="18" t="inlineStr">
+        <is>
+          <t>Srikanth Nori</t>
+        </is>
+      </c>
+      <c r="O157" s="18" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Managing Director</t>
+        </is>
+      </c>
       <c r="P157" s="18" t="inlineStr"/>
       <c r="Q157" s="18" t="inlineStr"/>
-      <c r="R157" s="18" t="inlineStr"/>
+      <c r="R157" s="18" t="inlineStr">
+        <is>
+          <t>+91 40 4015 5251</t>
+        </is>
+      </c>
       <c r="S157" s="17" t="inlineStr">
         <is>
-          <t>visualhash.tech</t>
-        </is>
-      </c>
-      <c r="T157" s="18" t="inlineStr"/>
+          <t>geovista.in</t>
+        </is>
+      </c>
+      <c r="T157" s="17" t="inlineStr">
+        <is>
+          <t>contact@geovista.in</t>
+        </is>
+      </c>
       <c r="U157" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13640,16 +13656,16 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>GeoVista Technologies Pvt. Ltd.</t>
+          <t>TriCAD Design Consultants Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>geovista.in</t>
+          <t>tricadinfo.com</t>
         </is>
       </c>
       <c r="D158" s="11" t="n">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
@@ -13673,54 +13689,50 @@
       </c>
       <c r="I158" s="11" t="inlineStr">
         <is>
-          <t>201-500</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>Aerial photogrammetry services; UAV LiDAR scanning; topographic land surveying; GIS asset mapping</t>
+          <t>Drone data analytics software; aerial photogrammetry processing; 3D city modeling solutions</t>
         </is>
       </c>
       <c r="K158" s="14" t="inlineStr">
         <is>
-          <t>Turnkey geospatial data acquisition, highway network mapping, and railway asset monitoring.</t>
+          <t>LiDAR feature processing, engineering telemetry extraction, and aerial telecom network mapping.</t>
         </is>
       </c>
       <c r="L158" s="14" t="inlineStr">
         <is>
-          <t>UAV photogrammetry platforms, drone-mounted LiDAR arrays</t>
+          <t>UAV Master analytical workflows, Trimble Inpho aerial photogrammetry software, drone cloud mapping software</t>
         </is>
       </c>
       <c r="M158" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N158" s="14" t="inlineStr">
         <is>
-          <t>Srikanth Nori</t>
+          <t>Seshagiri Mangamuri</t>
         </is>
       </c>
       <c r="O158" s="14" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Director</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="P158" s="14" t="inlineStr"/>
       <c r="Q158" s="14" t="inlineStr"/>
-      <c r="R158" s="14" t="inlineStr">
-        <is>
-          <t>+91 40 4015 5251</t>
-        </is>
-      </c>
+      <c r="R158" s="14" t="inlineStr"/>
       <c r="S158" s="13" t="inlineStr">
         <is>
-          <t>geovista.in</t>
+          <t>tricadinfo.com</t>
         </is>
       </c>
       <c r="T158" s="13" t="inlineStr">
         <is>
-          <t>contact@geovista.in</t>
+          <t>cooperation@tricadinfo.com</t>
         </is>
       </c>
       <c r="U158" s="11" t="inlineStr">
@@ -13729,22 +13741,22 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="46.5" customHeight="1">
+    <row r="159" ht="33" customHeight="1">
       <c r="A159" s="15" t="n">
         <v>154</v>
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>TriCAD Design Consultants Pvt. Ltd.</t>
+          <t>Terraorbit Mapping Private Limited</t>
         </is>
       </c>
       <c r="C159" s="17" t="inlineStr">
         <is>
-          <t>tricadinfo.com</t>
+          <t>https://terraorbit.in</t>
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
@@ -13768,22 +13780,22 @@
       </c>
       <c r="I159" s="15" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J159" s="18" t="inlineStr">
         <is>
-          <t>Drone data analytics software; aerial photogrammetry processing; 3D city modeling solutions</t>
+          <t>Aerial LiDAR surveying; industrial site scanning; BIM engineering services</t>
         </is>
       </c>
       <c r="K159" s="18" t="inlineStr">
         <is>
-          <t>LiDAR feature processing, engineering telemetry extraction, and aerial telecom network mapping.</t>
+          <t>3D point cloud intelligence for power and bulk drug infrastructure sectors</t>
         </is>
       </c>
       <c r="L159" s="18" t="inlineStr">
         <is>
-          <t>UAV Master analytical workflows, Trimble Inpho aerial photogrammetry software, drone cloud mapping software</t>
+          <t>Sag and clearance analysis; vegetation encroachment detection; Scan-to-CAD workflows</t>
         </is>
       </c>
       <c r="M159" s="15" t="inlineStr">
@@ -13791,51 +13803,39 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N159" s="18" t="inlineStr">
-        <is>
-          <t>Seshagiri Mangamuri</t>
-        </is>
-      </c>
-      <c r="O159" s="18" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
+      <c r="N159" s="18" t="inlineStr"/>
+      <c r="O159" s="18" t="inlineStr"/>
       <c r="P159" s="18" t="inlineStr"/>
       <c r="Q159" s="18" t="inlineStr"/>
       <c r="R159" s="18" t="inlineStr"/>
       <c r="S159" s="17" t="inlineStr">
         <is>
-          <t>tricadinfo.com</t>
-        </is>
-      </c>
-      <c r="T159" s="17" t="inlineStr">
-        <is>
-          <t>cooperation@tricadinfo.com</t>
-        </is>
-      </c>
+          <t>https://terraorbit.in</t>
+        </is>
+      </c>
+      <c r="T159" s="18" t="inlineStr"/>
       <c r="U159" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="33" customHeight="1">
+    <row r="160" ht="46.5" customHeight="1">
       <c r="A160" s="11" t="n">
         <v>155</v>
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>Terraorbit Mapping Private Limited</t>
+          <t>Santop Technologies LLP</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>https://terraorbit.in</t>
+          <t>https://santoptech.com</t>
         </is>
       </c>
       <c r="D160" s="11" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
@@ -13864,17 +13864,17 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>Aerial LiDAR surveying; industrial site scanning; BIM engineering services</t>
+          <t>Geospatial drone surveying; 3D laser scanning; cadastral and topographic mapping</t>
         </is>
       </c>
       <c r="K160" s="14" t="inlineStr">
         <is>
-          <t>3D point cloud intelligence for power and bulk drug infrastructure sectors</t>
+          <t>Multi-technique engineering land surveys and civil consultancy</t>
         </is>
       </c>
       <c r="L160" s="14" t="inlineStr">
         <is>
-          <t>Sag and clearance analysis; vegetation encroachment detection; Scan-to-CAD workflows</t>
+          <t>RTK drone mapping; DGPS ground control surveys; LiDAR 3D scanning</t>
         </is>
       </c>
       <c r="M160" s="11" t="inlineStr">
@@ -13889,7 +13889,7 @@
       <c r="R160" s="14" t="inlineStr"/>
       <c r="S160" s="13" t="inlineStr">
         <is>
-          <t>https://terraorbit.in</t>
+          <t>https://santoptech.com</t>
         </is>
       </c>
       <c r="T160" s="14" t="inlineStr"/>
@@ -13899,26 +13899,26 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="46.5" customHeight="1">
+    <row r="161" ht="60" customHeight="1">
       <c r="A161" s="15" t="n">
         <v>156</v>
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>Santop Technologies LLP</t>
+          <t>DAERO Drone Services</t>
         </is>
       </c>
       <c r="C161" s="17" t="inlineStr">
         <is>
-          <t>https://santoptech.com</t>
+          <t>https://daero.in</t>
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="E161" s="18" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F161" s="18" t="inlineStr">
@@ -13943,17 +13943,17 @@
       </c>
       <c r="J161" s="18" t="inlineStr">
         <is>
-          <t>Geospatial drone surveying; 3D laser scanning; cadastral and topographic mapping</t>
+          <t>Agricultural spraying services; Aerial mapping and surveying services; LiDAR inspection services; Thermal inspection services</t>
         </is>
       </c>
       <c r="K161" s="18" t="inlineStr">
         <is>
-          <t>Multi-technique engineering land surveys and civil consultancy</t>
+          <t>Precision agricultural drone spraying and survey-grade workflows for industrial infrastructure and government clients.</t>
         </is>
       </c>
       <c r="L161" s="18" t="inlineStr">
         <is>
-          <t>RTK drone mapping; DGPS ground control surveys; LiDAR 3D scanning</t>
+          <t>Drone Spraying; Seed Broadcast; Crop Monitoring; LiDAR infrastructure mapping; Thermal inspection</t>
         </is>
       </c>
       <c r="M161" s="15" t="inlineStr">
@@ -13965,10 +13965,14 @@
       <c r="O161" s="18" t="inlineStr"/>
       <c r="P161" s="18" t="inlineStr"/>
       <c r="Q161" s="18" t="inlineStr"/>
-      <c r="R161" s="18" t="inlineStr"/>
+      <c r="R161" s="18" t="inlineStr">
+        <is>
+          <t>+91 95970 44786</t>
+        </is>
+      </c>
       <c r="S161" s="17" t="inlineStr">
         <is>
-          <t>https://santoptech.com</t>
+          <t>https://daero.in</t>
         </is>
       </c>
       <c r="T161" s="18" t="inlineStr"/>
@@ -13984,20 +13988,20 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>DAERO Drone Services</t>
+          <t>Aerosquad Pvt Ltd</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>https://daero.in</t>
+          <t>https://aerosquad.in</t>
         </is>
       </c>
       <c r="D162" s="11" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F162" s="14" t="inlineStr">
@@ -14017,22 +14021,22 @@
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>Agricultural spraying services; Aerial mapping and surveying services; LiDAR inspection services; Thermal inspection services</t>
+          <t>Aerial drone land surveys; UAV data processing services; Solar thermography inspection; Agricultural NDVI monitoring</t>
         </is>
       </c>
       <c r="K162" s="14" t="inlineStr">
         <is>
-          <t>Precision agricultural drone spraying and survey-grade workflows for industrial infrastructure and government clients.</t>
+          <t>Utilizing simultaneous total facility and company-grade DGPS base stations with RTK drones for high-precision land record verification.</t>
         </is>
       </c>
       <c r="L162" s="14" t="inlineStr">
         <is>
-          <t>Drone Spraying; Seed Broadcast; Crop Monitoring; LiDAR infrastructure mapping; Thermal inspection</t>
+          <t>RTK Drones; DGPS base stations; 2D/3D Orthomosaic Maps; Digital Elevation Models; Thermal Imaging</t>
         </is>
       </c>
       <c r="M162" s="11" t="inlineStr">
@@ -14040,21 +14044,33 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N162" s="14" t="inlineStr"/>
-      <c r="O162" s="14" t="inlineStr"/>
+      <c r="N162" s="14" t="inlineStr">
+        <is>
+          <t>Aravindharajan G</t>
+        </is>
+      </c>
+      <c r="O162" s="14" t="inlineStr">
+        <is>
+          <t>Chief Operations Officer</t>
+        </is>
+      </c>
       <c r="P162" s="14" t="inlineStr"/>
       <c r="Q162" s="14" t="inlineStr"/>
       <c r="R162" s="14" t="inlineStr">
         <is>
-          <t>+91 95970 44786</t>
+          <t>+91 74022 24560</t>
         </is>
       </c>
       <c r="S162" s="13" t="inlineStr">
         <is>
-          <t>https://daero.in</t>
-        </is>
-      </c>
-      <c r="T162" s="14" t="inlineStr"/>
+          <t>https://aerosquad.in</t>
+        </is>
+      </c>
+      <c r="T162" s="13" t="inlineStr">
+        <is>
+          <t>support@aerosquad.com</t>
+        </is>
+      </c>
       <c r="U162" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14067,20 +14083,20 @@
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>Aerosquad Pvt Ltd</t>
+          <t>Aero360</t>
         </is>
       </c>
       <c r="C163" s="17" t="inlineStr">
         <is>
-          <t>https://aerosquad.in</t>
+          <t>https://aero360.co.in</t>
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F163" s="18" t="inlineStr">
@@ -14105,17 +14121,17 @@
       </c>
       <c r="J163" s="18" t="inlineStr">
         <is>
-          <t>Aerial drone land surveys; UAV data processing services; Solar thermography inspection; Agricultural NDVI monitoring</t>
+          <t>Custom industrial enterprise drones; Tactical security surveillance drones; Aerial pipeline corridor mapping; Specialized drone pilot certification</t>
         </is>
       </c>
       <c r="K163" s="18" t="inlineStr">
         <is>
-          <t>Utilizing simultaneous total facility and company-grade DGPS base stations with RTK drones for high-precision land record verification.</t>
+          <t>Designing and deploying high-endurance heavy-lift UAV solutions for defense, mining, and oil &amp; gas pipeline asset tracking.</t>
         </is>
       </c>
       <c r="L163" s="18" t="inlineStr">
         <is>
-          <t>RTK Drones; DGPS base stations; 2D/3D Orthomosaic Maps; Digital Elevation Models; Thermal Imaging</t>
+          <t>Vajra-S modular UAV; BhumiA10E drone; Vyoma-S long-range drone; Thermal night-vision camera payloads</t>
         </is>
       </c>
       <c r="M163" s="15" t="inlineStr">
@@ -14125,29 +14141,29 @@
       </c>
       <c r="N163" s="18" t="inlineStr">
         <is>
-          <t>Aravindharajan G</t>
+          <t>Pragadish Santhosh A</t>
         </is>
       </c>
       <c r="O163" s="18" t="inlineStr">
         <is>
-          <t>Chief Operations Officer</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="P163" s="18" t="inlineStr"/>
       <c r="Q163" s="18" t="inlineStr"/>
       <c r="R163" s="18" t="inlineStr">
         <is>
-          <t>+91 74022 24560</t>
+          <t>+91 78459 08931</t>
         </is>
       </c>
       <c r="S163" s="17" t="inlineStr">
         <is>
-          <t>https://aerosquad.in</t>
+          <t>https://aero360.co.in</t>
         </is>
       </c>
       <c r="T163" s="17" t="inlineStr">
         <is>
-          <t>support@aerosquad.com</t>
+          <t>marketing@aero360.co.in</t>
         </is>
       </c>
       <c r="U163" s="15" t="inlineStr">
@@ -14156,22 +14172,22 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
+    <row r="164" ht="33" customHeight="1">
       <c r="A164" s="11" t="n">
         <v>159</v>
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>Aero360</t>
+          <t>AEROKNOTZ</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>https://aero360.co.in</t>
+          <t>https://aeroknotz.com</t>
         </is>
       </c>
       <c r="D164" s="11" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
@@ -14200,17 +14216,17 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>Custom industrial enterprise drones; Tactical security surveillance drones; Aerial pipeline corridor mapping; Specialized drone pilot certification</t>
+          <t>Drone training courses; industrial aerial surveying and inspection</t>
         </is>
       </c>
       <c r="K164" s="14" t="inlineStr">
         <is>
-          <t>Designing and deploying high-endurance heavy-lift UAV solutions for defense, mining, and oil &amp; gas pipeline asset tracking.</t>
+          <t>UAV technology vocational education and enterprise aerial mapping projects</t>
         </is>
       </c>
       <c r="L164" s="14" t="inlineStr">
         <is>
-          <t>Vajra-S modular UAV; BhumiA10E drone; Vyoma-S long-range drone; Thermal night-vision camera payloads</t>
+          <t>Aerial cinematography; mapping and inspection drones; flight simulators</t>
         </is>
       </c>
       <c r="M164" s="11" t="inlineStr">
@@ -14218,33 +14234,17 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N164" s="14" t="inlineStr">
-        <is>
-          <t>Pragadish Santhosh A</t>
-        </is>
-      </c>
-      <c r="O164" s="14" t="inlineStr">
-        <is>
-          <t>Chief Technology Officer</t>
-        </is>
-      </c>
+      <c r="N164" s="14" t="inlineStr"/>
+      <c r="O164" s="14" t="inlineStr"/>
       <c r="P164" s="14" t="inlineStr"/>
       <c r="Q164" s="14" t="inlineStr"/>
-      <c r="R164" s="14" t="inlineStr">
-        <is>
-          <t>+91 78459 08931</t>
-        </is>
-      </c>
+      <c r="R164" s="14" t="inlineStr"/>
       <c r="S164" s="13" t="inlineStr">
         <is>
-          <t>https://aero360.co.in</t>
-        </is>
-      </c>
-      <c r="T164" s="13" t="inlineStr">
-        <is>
-          <t>marketing@aero360.co.in</t>
-        </is>
-      </c>
+          <t>https://aeroknotz.com</t>
+        </is>
+      </c>
+      <c r="T164" s="14" t="inlineStr"/>
       <c r="U164" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14257,20 +14257,20 @@
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>AEROKNOTZ</t>
+          <t>cymatics.in</t>
         </is>
       </c>
       <c r="C165" s="17" t="inlineStr">
         <is>
-          <t>https://aeroknotz.com</t>
+          <t>https://cymatics.in</t>
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F165" s="18" t="inlineStr">
@@ -14285,27 +14285,27 @@
       </c>
       <c r="H165" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="J165" s="18" t="inlineStr">
         <is>
-          <t>Drone training courses; industrial aerial surveying and inspection</t>
+          <t>Aerial filming and media production; geospatial photogrammetry mapping</t>
         </is>
       </c>
       <c r="K165" s="18" t="inlineStr">
         <is>
-          <t>UAV technology vocational education and enterprise aerial mapping projects</t>
+          <t>High-definition aerial cinematography and precision-driven industrial mapping analytics</t>
         </is>
       </c>
       <c r="L165" s="18" t="inlineStr">
         <is>
-          <t>Aerial cinematography; mapping and inspection drones; flight simulators</t>
+          <t>360 HDR photography; Orthomosaic mapping; wildlife surveillance thermal drone analytics</t>
         </is>
       </c>
       <c r="M165" s="15" t="inlineStr">
@@ -14317,13 +14317,21 @@
       <c r="O165" s="18" t="inlineStr"/>
       <c r="P165" s="18" t="inlineStr"/>
       <c r="Q165" s="18" t="inlineStr"/>
-      <c r="R165" s="18" t="inlineStr"/>
+      <c r="R165" s="18" t="inlineStr">
+        <is>
+          <t>+91 93441 05768</t>
+        </is>
+      </c>
       <c r="S165" s="17" t="inlineStr">
         <is>
-          <t>https://aeroknotz.com</t>
-        </is>
-      </c>
-      <c r="T165" s="18" t="inlineStr"/>
+          <t>https://cymatics.in</t>
+        </is>
+      </c>
+      <c r="T165" s="17" t="inlineStr">
+        <is>
+          <t>marketing@cymatics.in</t>
+        </is>
+      </c>
       <c r="U165" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14336,12 +14344,12 @@
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>cymatics.in</t>
+          <t>De drone world solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>https://cymatics.in</t>
+          <t>thedroneworld.in</t>
         </is>
       </c>
       <c r="D166" s="11" t="n">
@@ -14364,27 +14372,27 @@
       </c>
       <c r="H166" s="14" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I166" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>Aerial filming and media production; geospatial photogrammetry mapping</t>
+          <t>DGCA certified drone pilot courses; agricultural precision drone services</t>
         </is>
       </c>
       <c r="K166" s="14" t="inlineStr">
         <is>
-          <t>High-definition aerial cinematography and precision-driven industrial mapping analytics</t>
+          <t>Aviation-grade drone training, technical workshops, and enterprise aerial mapping</t>
         </is>
       </c>
       <c r="L166" s="14" t="inlineStr">
         <is>
-          <t>360 HDR photography; Orthomosaic mapping; wildlife surveillance thermal drone analytics</t>
+          <t>Remote Pilot Certificate (RPC) programs; agricultural spraying drones</t>
         </is>
       </c>
       <c r="M166" s="11" t="inlineStr">
@@ -14396,21 +14404,13 @@
       <c r="O166" s="14" t="inlineStr"/>
       <c r="P166" s="14" t="inlineStr"/>
       <c r="Q166" s="14" t="inlineStr"/>
-      <c r="R166" s="14" t="inlineStr">
-        <is>
-          <t>+91 93441 05768</t>
-        </is>
-      </c>
+      <c r="R166" s="14" t="inlineStr"/>
       <c r="S166" s="13" t="inlineStr">
         <is>
-          <t>https://cymatics.in</t>
-        </is>
-      </c>
-      <c r="T166" s="13" t="inlineStr">
-        <is>
-          <t>marketing@cymatics.in</t>
-        </is>
-      </c>
+          <t>thedroneworld.in</t>
+        </is>
+      </c>
+      <c r="T166" s="14" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14423,16 +14423,16 @@
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>De drone world solutions Pvt Ltd</t>
+          <t>Skywalk Drobotics Academy</t>
         </is>
       </c>
       <c r="C167" s="17" t="inlineStr">
         <is>
-          <t>thedroneworld.in</t>
+          <t>http://www.skywalkdrobotics.com</t>
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
@@ -14461,17 +14461,17 @@
       </c>
       <c r="J167" s="18" t="inlineStr">
         <is>
-          <t>DGCA certified drone pilot courses; agricultural precision drone services</t>
+          <t>Drone flight education; aerial filming and robotic training programs</t>
         </is>
       </c>
       <c r="K167" s="18" t="inlineStr">
         <is>
-          <t>Aviation-grade drone training, technical workshops, and enterprise aerial mapping</t>
+          <t>Practical drone pilot certification and academic STEM robotics workshops</t>
         </is>
       </c>
       <c r="L167" s="18" t="inlineStr">
         <is>
-          <t>Remote Pilot Certificate (RPC) programs; agricultural spraying drones</t>
+          <t>Unmanned Aerial Vehicle (UAV) flight training setups; FPV simulation tools</t>
         </is>
       </c>
       <c r="M167" s="15" t="inlineStr">
@@ -14483,39 +14483,47 @@
       <c r="O167" s="18" t="inlineStr"/>
       <c r="P167" s="18" t="inlineStr"/>
       <c r="Q167" s="18" t="inlineStr"/>
-      <c r="R167" s="18" t="inlineStr"/>
+      <c r="R167" s="18" t="inlineStr">
+        <is>
+          <t>+91 97902 11002</t>
+        </is>
+      </c>
       <c r="S167" s="17" t="inlineStr">
         <is>
-          <t>thedroneworld.in</t>
-        </is>
-      </c>
-      <c r="T167" s="18" t="inlineStr"/>
+          <t>http://www.skywalkdrobotics.com</t>
+        </is>
+      </c>
+      <c r="T167" s="17" t="inlineStr">
+        <is>
+          <t>support@skywalkdrobotics.com</t>
+        </is>
+      </c>
       <c r="U167" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="33" customHeight="1">
+    <row r="168" ht="46.5" customHeight="1">
       <c r="A168" s="11" t="n">
         <v>163</v>
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>Skywalk Drobotics Academy</t>
+          <t>Anvation Drones and Research Technologies Private limited</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>http://www.skywalkdrobotics.com</t>
+          <t>https://anvationdrones.com</t>
         </is>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F168" s="14" t="inlineStr">
@@ -14540,17 +14548,17 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>Drone flight education; aerial filming and robotic training programs</t>
+          <t>High-precision mapping and inspection services; R&amp;D defense engineering solutions</t>
         </is>
       </c>
       <c r="K168" s="14" t="inlineStr">
         <is>
-          <t>Practical drone pilot certification and academic STEM robotics workshops</t>
+          <t>RGB, LiDAR, and thermal drone mapping alongside cargo delivery research</t>
         </is>
       </c>
       <c r="L168" s="14" t="inlineStr">
         <is>
-          <t>Unmanned Aerial Vehicle (UAV) flight training setups; FPV simulation tools</t>
+          <t>Enterprise-grade mapping drones; anti-drone system architectures; thermal highway inspection imaging</t>
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr">
@@ -14562,21 +14570,13 @@
       <c r="O168" s="14" t="inlineStr"/>
       <c r="P168" s="14" t="inlineStr"/>
       <c r="Q168" s="14" t="inlineStr"/>
-      <c r="R168" s="14" t="inlineStr">
-        <is>
-          <t>+91 97902 11002</t>
-        </is>
-      </c>
+      <c r="R168" s="14" t="inlineStr"/>
       <c r="S168" s="13" t="inlineStr">
         <is>
-          <t>http://www.skywalkdrobotics.com</t>
-        </is>
-      </c>
-      <c r="T168" s="13" t="inlineStr">
-        <is>
-          <t>support@skywalkdrobotics.com</t>
-        </is>
-      </c>
+          <t>https://anvationdrones.com</t>
+        </is>
+      </c>
+      <c r="T168" s="14" t="inlineStr"/>
       <c r="U168" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14589,20 +14589,20 @@
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>Anvation Drones and Research Technologies Private limited</t>
+          <t>Syfero Synergetics Tech Solutions (P) Ltd</t>
         </is>
       </c>
       <c r="C169" s="17" t="inlineStr">
         <is>
-          <t>https://anvationdrones.com</t>
+          <t>https://syfero.com</t>
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E169" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F169" s="18" t="inlineStr">
@@ -14627,17 +14627,17 @@
       </c>
       <c r="J169" s="18" t="inlineStr">
         <is>
-          <t>High-precision mapping and inspection services; R&amp;D defense engineering solutions</t>
+          <t>Agricultural spraying drones; drone components and MRO technical services</t>
         </is>
       </c>
       <c r="K169" s="18" t="inlineStr">
         <is>
-          <t>RGB, LiDAR, and thermal drone mapping alongside cargo delivery research</t>
+          <t>End-to-end commercial agricultural drone workflows and technical field support for farmers</t>
         </is>
       </c>
       <c r="L169" s="18" t="inlineStr">
         <is>
-          <t>Enterprise-grade mapping drones; anti-drone system architectures; thermal highway inspection imaging</t>
+          <t>Beta 610, Phoenix 30L, Raptor 10L, and Syfer-X 20L spraying drones; drone telemetry check systems</t>
         </is>
       </c>
       <c r="M169" s="15" t="inlineStr">
@@ -14649,13 +14649,21 @@
       <c r="O169" s="18" t="inlineStr"/>
       <c r="P169" s="18" t="inlineStr"/>
       <c r="Q169" s="18" t="inlineStr"/>
-      <c r="R169" s="18" t="inlineStr"/>
+      <c r="R169" s="18" t="inlineStr">
+        <is>
+          <t>+91 98943 25456</t>
+        </is>
+      </c>
       <c r="S169" s="17" t="inlineStr">
         <is>
-          <t>https://anvationdrones.com</t>
-        </is>
-      </c>
-      <c r="T169" s="18" t="inlineStr"/>
+          <t>https://syfero.com</t>
+        </is>
+      </c>
+      <c r="T169" s="17" t="inlineStr">
+        <is>
+          <t>sales@syfero.com</t>
+        </is>
+      </c>
       <c r="U169" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14668,16 +14676,16 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>Syfero Synergetics Tech Solutions (P) Ltd</t>
+          <t>SKYX AEROSPACE PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>https://syfero.com</t>
+          <t>https://skyx.co.in</t>
         </is>
       </c>
       <c r="D170" s="11" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
@@ -14701,22 +14709,22 @@
       </c>
       <c r="I170" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>Agricultural spraying drones; drone components and MRO technical services</t>
+          <t>Industrial and agricultural unmanned aerial vehicles; geospatial GIS analytics tools</t>
         </is>
       </c>
       <c r="K170" s="14" t="inlineStr">
         <is>
-          <t>End-to-end commercial agricultural drone workflows and technical field support for farmers</t>
+          <t>Drone-as-a-Service (DaaS) delivery model leveraging specialized high-zoom hardware options</t>
         </is>
       </c>
       <c r="L170" s="14" t="inlineStr">
         <is>
-          <t>Beta 610, Phoenix 30L, Raptor 10L, and Syfer-X 20L spraying drones; drone telemetry check systems</t>
+          <t>SKYX KISAAN agri drones; 180x+ optical zoom variant monitoring modules; advanced 3D modelling systems</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr">
@@ -14730,17 +14738,17 @@
       <c r="Q170" s="14" t="inlineStr"/>
       <c r="R170" s="14" t="inlineStr">
         <is>
-          <t>+91 98943 25456</t>
+          <t>+91 82200 13957</t>
         </is>
       </c>
       <c r="S170" s="13" t="inlineStr">
         <is>
-          <t>https://syfero.com</t>
+          <t>https://skyx.co.in</t>
         </is>
       </c>
       <c r="T170" s="13" t="inlineStr">
         <is>
-          <t>sales@syfero.com</t>
+          <t>info@skyx.co.in</t>
         </is>
       </c>
       <c r="U170" s="11" t="inlineStr">
@@ -14755,20 +14763,20 @@
       </c>
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>SKYX AEROSPACE PRIVATE LIMITED</t>
+          <t>Vayu Drone Services Private Limited</t>
         </is>
       </c>
       <c r="C171" s="17" t="inlineStr">
         <is>
-          <t>https://skyx.co.in</t>
+          <t>vayudrones.in</t>
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F171" s="18" t="inlineStr">
@@ -14788,22 +14796,22 @@
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J171" s="18" t="inlineStr">
         <is>
-          <t>Industrial and agricultural unmanned aerial vehicles; geospatial GIS analytics tools</t>
+          <t>Agricultural drone spraying; farm monitoring services</t>
         </is>
       </c>
       <c r="K171" s="18" t="inlineStr">
         <is>
-          <t>Drone-as-a-Service (DaaS) delivery model leveraging specialized high-zoom hardware options</t>
+          <t>Precision agricultural drone technology, chemical and nutrient spraying, and crop analytics</t>
         </is>
       </c>
       <c r="L171" s="18" t="inlineStr">
         <is>
-          <t>SKYX KISAAN agri drones; 180x+ optical zoom variant monitoring modules; advanced 3D modelling systems</t>
+          <t>GPS-equipped agricultural spraying multirotors and precision flight control software</t>
         </is>
       </c>
       <c r="M171" s="15" t="inlineStr">
@@ -14817,17 +14825,17 @@
       <c r="Q171" s="18" t="inlineStr"/>
       <c r="R171" s="18" t="inlineStr">
         <is>
-          <t>+91 82200 13957</t>
+          <t>+917448304888</t>
         </is>
       </c>
       <c r="S171" s="17" t="inlineStr">
         <is>
-          <t>https://skyx.co.in</t>
+          <t>vayudrones.in</t>
         </is>
       </c>
       <c r="T171" s="17" t="inlineStr">
         <is>
-          <t>info@skyx.co.in</t>
+          <t>cc@vayudrones.in</t>
         </is>
       </c>
       <c r="U171" s="15" t="inlineStr">
@@ -14842,12 +14850,12 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t>Vayu Drone Services Private Limited</t>
+          <t>Sri Eshwar Drone Tech Private Limited</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>vayudrones.in</t>
+          <t>sedt.ac.in</t>
         </is>
       </c>
       <c r="D172" s="11" t="n">
@@ -14855,7 +14863,7 @@
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F172" s="14" t="inlineStr">
@@ -14875,22 +14883,22 @@
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone spraying; farm monitoring services</t>
+          <t>Remote pilot training; drone certification courses</t>
         </is>
       </c>
       <c r="K172" s="14" t="inlineStr">
         <is>
-          <t>Precision agricultural drone technology, chemical and nutrient spraying, and crop analytics</t>
+          <t>DGCA-approved commercial remote pilot certificate courses for small and medium class drones</t>
         </is>
       </c>
       <c r="L172" s="14" t="inlineStr">
         <is>
-          <t>GPS-equipped agricultural spraying multirotors and precision flight control software</t>
+          <t>Flight simulator training, flight training multirotors, and micro/small class drone regulations</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr">
@@ -14904,19 +14912,15 @@
       <c r="Q172" s="14" t="inlineStr"/>
       <c r="R172" s="14" t="inlineStr">
         <is>
-          <t>+917448304888</t>
+          <t>+919500635060</t>
         </is>
       </c>
       <c r="S172" s="13" t="inlineStr">
         <is>
-          <t>vayudrones.in</t>
-        </is>
-      </c>
-      <c r="T172" s="13" t="inlineStr">
-        <is>
-          <t>cc@vayudrones.in</t>
-        </is>
-      </c>
+          <t>sedt.ac.in</t>
+        </is>
+      </c>
+      <c r="T172" s="14" t="inlineStr"/>
       <c r="U172" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14929,20 +14933,20 @@
       </c>
       <c r="B173" s="16" t="inlineStr">
         <is>
-          <t>Sri Eshwar Drone Tech Private Limited</t>
+          <t>Mars Synergy Geo Tech Private Limited</t>
         </is>
       </c>
       <c r="C173" s="17" t="inlineStr">
         <is>
-          <t>sedt.ac.in</t>
+          <t>marssynergygeotech.com</t>
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>2023</v>
+        <v>2009</v>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F173" s="18" t="inlineStr">
@@ -14962,22 +14966,22 @@
       </c>
       <c r="I173" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J173" s="18" t="inlineStr">
         <is>
-          <t>Remote pilot training; drone certification courses</t>
+          <t>Drone mapping surveys; topographic land surveying</t>
         </is>
       </c>
       <c r="K173" s="18" t="inlineStr">
         <is>
-          <t>DGCA-approved commercial remote pilot certificate courses for small and medium class drones</t>
+          <t>High-precision commercial terrain mapping, rooftop analysis, and geotechnical engineering surveys</t>
         </is>
       </c>
       <c r="L173" s="18" t="inlineStr">
         <is>
-          <t>Flight simulator training, flight training multirotors, and micro/small class drone regulations</t>
+          <t>Fixed-wing and multicopter UAV data acquisition, photogrammetry tools, and AutoCAD integrations</t>
         </is>
       </c>
       <c r="M173" s="15" t="inlineStr">
@@ -14985,18 +14989,26 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N173" s="18" t="inlineStr"/>
-      <c r="O173" s="18" t="inlineStr"/>
+      <c r="N173" s="18" t="inlineStr">
+        <is>
+          <t>Baskar</t>
+        </is>
+      </c>
+      <c r="O173" s="18" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="P173" s="18" t="inlineStr"/>
       <c r="Q173" s="18" t="inlineStr"/>
       <c r="R173" s="18" t="inlineStr">
         <is>
-          <t>+919500635060</t>
+          <t>+917942557489</t>
         </is>
       </c>
       <c r="S173" s="17" t="inlineStr">
         <is>
-          <t>sedt.ac.in</t>
+          <t>marssynergygeotech.com</t>
         </is>
       </c>
       <c r="T173" s="18" t="inlineStr"/>
@@ -15012,16 +15024,16 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t>Mars Synergy Geo Tech Private Limited</t>
+          <t>Leadingedge Futuring Technology Private Limited</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>marssynergygeotech.com</t>
+          <t>leadingedgeft.com</t>
         </is>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
@@ -15050,17 +15062,17 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>Drone mapping surveys; topographic land surveying</t>
+          <t>Drone aerial inspection; agricultural crop spraying services</t>
         </is>
       </c>
       <c r="K174" s="14" t="inlineStr">
         <is>
-          <t>High-precision commercial terrain mapping, rooftop analysis, and geotechnical engineering surveys</t>
+          <t>High-precision infrastructure, power grid, solar installation inspections, and automated delivery testing</t>
         </is>
       </c>
       <c r="L174" s="14" t="inlineStr">
         <is>
-          <t>Fixed-wing and multicopter UAV data acquisition, photogrammetry tools, and AutoCAD integrations</t>
+          <t>Enterprise-grade mapping drones, delivery drone configurations, and agricultural spray multirotors</t>
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr">
@@ -15070,24 +15082,24 @@
       </c>
       <c r="N174" s="14" t="inlineStr">
         <is>
-          <t>Baskar</t>
+          <t>Gobinath</t>
         </is>
       </c>
       <c r="O174" s="14" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Project engineer</t>
         </is>
       </c>
       <c r="P174" s="14" t="inlineStr"/>
       <c r="Q174" s="14" t="inlineStr"/>
       <c r="R174" s="14" t="inlineStr">
         <is>
-          <t>+917942557489</t>
+          <t>+917942635061</t>
         </is>
       </c>
       <c r="S174" s="13" t="inlineStr">
         <is>
-          <t>marssynergygeotech.com</t>
+          <t>leadingedgeft.com</t>
         </is>
       </c>
       <c r="T174" s="14" t="inlineStr"/>
@@ -15103,16 +15115,16 @@
       </c>
       <c r="B175" s="16" t="inlineStr">
         <is>
-          <t>Leadingedge Futuring Technology Private Limited</t>
+          <t>Pentagon Infrastructures</t>
         </is>
       </c>
       <c r="C175" s="17" t="inlineStr">
         <is>
-          <t>leadingedgeft.com</t>
+          <t>pentagongroup.org</t>
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
@@ -15141,17 +15153,17 @@
       </c>
       <c r="J175" s="18" t="inlineStr">
         <is>
-          <t>Drone aerial inspection; agricultural crop spraying services</t>
+          <t>Aerial drone mapping; construction site topography</t>
         </is>
       </c>
       <c r="K175" s="18" t="inlineStr">
         <is>
-          <t>High-precision infrastructure, power grid, solar installation inspections, and automated delivery testing</t>
+          <t>Large industrial plot aerial mapping, digital contour mapping, and infrastructure project site verification</t>
         </is>
       </c>
       <c r="L175" s="18" t="inlineStr">
         <is>
-          <t>Enterprise-grade mapping drones, delivery drone configurations, and agricultural spray multirotors</t>
+          <t>Lithium-based enterprise surveillance drones, high-resolution aerial cameras, and 3D terrain modeling software</t>
         </is>
       </c>
       <c r="M175" s="15" t="inlineStr">
@@ -15159,29 +15171,25 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N175" s="18" t="inlineStr">
-        <is>
-          <t>Gobinath</t>
-        </is>
-      </c>
-      <c r="O175" s="18" t="inlineStr">
-        <is>
-          <t>Project engineer</t>
-        </is>
-      </c>
+      <c r="N175" s="18" t="inlineStr"/>
+      <c r="O175" s="18" t="inlineStr"/>
       <c r="P175" s="18" t="inlineStr"/>
       <c r="Q175" s="18" t="inlineStr"/>
       <c r="R175" s="18" t="inlineStr">
         <is>
-          <t>+917942635061</t>
+          <t>+919884527057</t>
         </is>
       </c>
       <c r="S175" s="17" t="inlineStr">
         <is>
-          <t>leadingedgeft.com</t>
-        </is>
-      </c>
-      <c r="T175" s="18" t="inlineStr"/>
+          <t>pentagongroup.org</t>
+        </is>
+      </c>
+      <c r="T175" s="17" t="inlineStr">
+        <is>
+          <t>pentagoninfraa@gmail.com</t>
+        </is>
+      </c>
       <c r="U175" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -15194,12 +15202,12 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t>Pentagon Infrastructures</t>
+          <t>JVR Land Surveys</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>pentagongroup.org</t>
+          <t>jvrlandsurveys.com</t>
         </is>
       </c>
       <c r="D176" s="11" t="n">
@@ -15232,17 +15240,17 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>Aerial drone mapping; construction site topography</t>
+          <t>Aerial drone photogrammetry; volume calculation services</t>
         </is>
       </c>
       <c r="K176" s="14" t="inlineStr">
         <is>
-          <t>Large industrial plot aerial mapping, digital contour mapping, and infrastructure project site verification</t>
+          <t>High-precision boundary mapping, infrastructure corridor tracking, and volume estimation using drones</t>
         </is>
       </c>
       <c r="L176" s="14" t="inlineStr">
         <is>
-          <t>Lithium-based enterprise surveillance drones, high-resolution aerial cameras, and 3D terrain modeling software</t>
+          <t>GPS and LiDAR-enabled mapping UAVs, digital mapping suites, and high-resolution orthomosaic engines</t>
         </is>
       </c>
       <c r="M176" s="11" t="inlineStr">
@@ -15256,17 +15264,17 @@
       <c r="Q176" s="14" t="inlineStr"/>
       <c r="R176" s="14" t="inlineStr">
         <is>
-          <t>+919884527057</t>
+          <t>+919940185722</t>
         </is>
       </c>
       <c r="S176" s="13" t="inlineStr">
         <is>
-          <t>pentagongroup.org</t>
+          <t>jvrlandsurveys.com</t>
         </is>
       </c>
       <c r="T176" s="13" t="inlineStr">
         <is>
-          <t>pentagoninfraa@gmail.com</t>
+          <t>jvrlandsurveys@gmail.com</t>
         </is>
       </c>
       <c r="U176" s="11" t="inlineStr">
@@ -15281,16 +15289,16 @@
       </c>
       <c r="B177" s="16" t="inlineStr">
         <is>
-          <t>JVR Land Surveys</t>
+          <t>Mithron India Smart Services Private Limited</t>
         </is>
       </c>
       <c r="C177" s="17" t="inlineStr">
         <is>
-          <t>jvrlandsurveys.com</t>
+          <t>mithron.co</t>
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
@@ -15304,7 +15312,7 @@
       </c>
       <c r="G177" s="18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; Malaysia</t>
         </is>
       </c>
       <c r="H177" s="18" t="inlineStr">
@@ -15319,17 +15327,17 @@
       </c>
       <c r="J177" s="18" t="inlineStr">
         <is>
-          <t>Aerial drone photogrammetry; volume calculation services</t>
+          <t>On-demand drone piloting services; agricultural flight bookings</t>
         </is>
       </c>
       <c r="K177" s="18" t="inlineStr">
         <is>
-          <t>High-precision boundary mapping, infrastructure corridor tracking, and volume estimation using drones</t>
+          <t>Aggregating digital ecosystems for on-demand agricultural plantation spray booking, logistics, and surveillance</t>
         </is>
       </c>
       <c r="L177" s="18" t="inlineStr">
         <is>
-          <t>GPS and LiDAR-enabled mapping UAVs, digital mapping suites, and high-resolution orthomosaic engines</t>
+          <t>ZRONEO city drone application, agricultural scheduling apps, and multi-brand drone tracking services</t>
         </is>
       </c>
       <c r="M177" s="15" t="inlineStr">
@@ -15337,51 +15345,51 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N177" s="18" t="inlineStr"/>
-      <c r="O177" s="18" t="inlineStr"/>
+      <c r="N177" s="18" t="inlineStr">
+        <is>
+          <t>Rajesh Krishnan</t>
+        </is>
+      </c>
+      <c r="O177" s="18" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
       <c r="P177" s="18" t="inlineStr"/>
       <c r="Q177" s="18" t="inlineStr"/>
-      <c r="R177" s="18" t="inlineStr">
-        <is>
-          <t>+919940185722</t>
-        </is>
-      </c>
+      <c r="R177" s="18" t="inlineStr"/>
       <c r="S177" s="17" t="inlineStr">
         <is>
-          <t>jvrlandsurveys.com</t>
-        </is>
-      </c>
-      <c r="T177" s="17" t="inlineStr">
-        <is>
-          <t>jvrlandsurveys@gmail.com</t>
-        </is>
-      </c>
+          <t>mithron.co</t>
+        </is>
+      </c>
+      <c r="T177" s="18" t="inlineStr"/>
       <c r="U177" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="46.5" customHeight="1">
+    <row r="178" ht="33" customHeight="1">
       <c r="A178" s="11" t="n">
         <v>173</v>
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t>Mithron India Smart Services Private Limited</t>
+          <t>JS Geospatial Solutions Private Limited</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>mithron.co</t>
+          <t>https://jsgeospatial.com</t>
         </is>
       </c>
       <c r="D178" s="11" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F178" s="14" t="inlineStr">
@@ -15391,7 +15399,7 @@
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
-          <t>India; Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr">
@@ -15406,17 +15414,17 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>On-demand drone piloting services; agricultural flight bookings</t>
+          <t>UAV aerial mapping; 3D topography modeling</t>
         </is>
       </c>
       <c r="K178" s="14" t="inlineStr">
         <is>
-          <t>Aggregating digital ecosystems for on-demand agricultural plantation spray booking, logistics, and surveillance</t>
+          <t>Drone-based surficial geo-data collection and hydrological analysis</t>
         </is>
       </c>
       <c r="L178" s="14" t="inlineStr">
         <is>
-          <t>ZRONEO city drone application, agricultural scheduling apps, and multi-brand drone tracking services</t>
+          <t>Drone photogrammetry, volumetric analysis algorithms</t>
         </is>
       </c>
       <c r="M178" s="11" t="inlineStr">
@@ -15426,23 +15434,35 @@
       </c>
       <c r="N178" s="14" t="inlineStr">
         <is>
-          <t>Rajesh Krishnan</t>
+          <t>V. Joevivek</t>
         </is>
       </c>
       <c r="O178" s="14" t="inlineStr">
         <is>
-          <t>Founder and CEO</t>
-        </is>
-      </c>
-      <c r="P178" s="14" t="inlineStr"/>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="P178" s="13" t="inlineStr">
+        <is>
+          <t>admin@jsgeospatial.com</t>
+        </is>
+      </c>
       <c r="Q178" s="14" t="inlineStr"/>
-      <c r="R178" s="14" t="inlineStr"/>
+      <c r="R178" s="14" t="inlineStr">
+        <is>
+          <t>+91 95852 53344</t>
+        </is>
+      </c>
       <c r="S178" s="13" t="inlineStr">
         <is>
-          <t>mithron.co</t>
-        </is>
-      </c>
-      <c r="T178" s="14" t="inlineStr"/>
+          <t>https://jsgeospatial.com</t>
+        </is>
+      </c>
+      <c r="T178" s="13" t="inlineStr">
+        <is>
+          <t>jsgeospatial@gmail.com</t>
+        </is>
+      </c>
       <c r="U178" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -15455,16 +15475,16 @@
       </c>
       <c r="B179" s="16" t="inlineStr">
         <is>
-          <t>JS Geospatial Solutions Private Limited</t>
+          <t>RVS Land Surveyors</t>
         </is>
       </c>
       <c r="C179" s="17" t="inlineStr">
         <is>
-          <t>https://jsgeospatial.com</t>
+          <t>rvslandsurveyors.com</t>
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E179" s="18" t="inlineStr">
         <is>
@@ -15483,7 +15503,7 @@
       </c>
       <c r="H179" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Partnership</t>
         </is>
       </c>
       <c r="I179" s="15" t="inlineStr">
@@ -15493,17 +15513,17 @@
       </c>
       <c r="J179" s="18" t="inlineStr">
         <is>
-          <t>UAV aerial mapping; 3D topography modeling</t>
+          <t>UAV topographic survey; boundary verification mapping</t>
         </is>
       </c>
       <c r="K179" s="18" t="inlineStr">
         <is>
-          <t>Drone-based surficial geo-data collection and hydrological analysis</t>
+          <t>Drone land surveys and cloud-based spatial data distribution</t>
         </is>
       </c>
       <c r="L179" s="18" t="inlineStr">
         <is>
-          <t>Drone photogrammetry, volumetric analysis algorithms</t>
+          <t>Photogrammetry software, aerial high-resolution orthomosaics</t>
         </is>
       </c>
       <c r="M179" s="15" t="inlineStr">
@@ -15511,37 +15531,17 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N179" s="18" t="inlineStr">
-        <is>
-          <t>V. Joevivek</t>
-        </is>
-      </c>
-      <c r="O179" s="18" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="P179" s="17" t="inlineStr">
-        <is>
-          <t>admin@jsgeospatial.com</t>
-        </is>
-      </c>
+      <c r="N179" s="18" t="inlineStr"/>
+      <c r="O179" s="18" t="inlineStr"/>
+      <c r="P179" s="18" t="inlineStr"/>
       <c r="Q179" s="18" t="inlineStr"/>
-      <c r="R179" s="18" t="inlineStr">
-        <is>
-          <t>+91 95852 53344</t>
-        </is>
-      </c>
+      <c r="R179" s="18" t="inlineStr"/>
       <c r="S179" s="17" t="inlineStr">
         <is>
-          <t>https://jsgeospatial.com</t>
-        </is>
-      </c>
-      <c r="T179" s="17" t="inlineStr">
-        <is>
-          <t>jsgeospatial@gmail.com</t>
-        </is>
-      </c>
+          <t>rvslandsurveyors.com</t>
+        </is>
+      </c>
+      <c r="T179" s="18" t="inlineStr"/>
       <c r="U179" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -15554,20 +15554,20 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t>RVS Land Surveyors</t>
+          <t>Birdscale Technology and Services Private Limited</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>rvslandsurveyors.com</t>
+          <t>https://birdscale.com</t>
         </is>
       </c>
       <c r="D180" s="11" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F180" s="14" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="H180" s="14" t="inlineStr">
         <is>
-          <t>Partnership</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I180" s="11" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>UAV topographic survey; boundary verification mapping</t>
+          <t>AI-driven mapping walkthroughs; corridor remote sensing</t>
         </is>
       </c>
       <c r="K180" s="14" t="inlineStr">
         <is>
-          <t>Drone land surveys and cloud-based spatial data distribution</t>
+          <t>ML-driven agricultural health mapping and infrastructure defect detection</t>
         </is>
       </c>
       <c r="L180" s="14" t="inlineStr">
         <is>
-          <t>Photogrammetry software, aerial high-resolution orthomosaics</t>
+          <t>BuildSafe project tracking software, computer vision inspection algorithms</t>
         </is>
       </c>
       <c r="M180" s="11" t="inlineStr">
@@ -15610,14 +15610,26 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N180" s="14" t="inlineStr"/>
-      <c r="O180" s="14" t="inlineStr"/>
+      <c r="N180" s="14" t="inlineStr">
+        <is>
+          <t>Hari Janarthanan</t>
+        </is>
+      </c>
+      <c r="O180" s="14" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
       <c r="P180" s="14" t="inlineStr"/>
       <c r="Q180" s="14" t="inlineStr"/>
-      <c r="R180" s="14" t="inlineStr"/>
+      <c r="R180" s="14" t="inlineStr">
+        <is>
+          <t>+91 82202 66060</t>
+        </is>
+      </c>
       <c r="S180" s="13" t="inlineStr">
         <is>
-          <t>rvslandsurveyors.com</t>
+          <t>https://birdscale.com</t>
         </is>
       </c>
       <c r="T180" s="14" t="inlineStr"/>
@@ -15633,16 +15645,16 @@
       </c>
       <c r="B181" s="16" t="inlineStr">
         <is>
-          <t>Birdscale Technology and Services Private Limited</t>
+          <t>L D R Survey Pvt Ltd</t>
         </is>
       </c>
       <c r="C181" s="17" t="inlineStr">
         <is>
-          <t>https://birdscale.com</t>
+          <t>https://ldrsurveys.com</t>
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="E181" s="18" t="inlineStr">
         <is>
@@ -15671,17 +15683,17 @@
       </c>
       <c r="J181" s="18" t="inlineStr">
         <is>
-          <t>AI-driven mapping walkthroughs; corridor remote sensing</t>
+          <t>UAV/LiDAR land surveys; as-built site modeling</t>
         </is>
       </c>
       <c r="K181" s="18" t="inlineStr">
         <is>
-          <t>ML-driven agricultural health mapping and infrastructure defect detection</t>
+          <t>Sub-centimeter precision drone topographic mapping for legal and banking use</t>
         </is>
       </c>
       <c r="L181" s="18" t="inlineStr">
         <is>
-          <t>BuildSafe project tracking software, computer vision inspection algorithms</t>
+          <t>DGCA-certified drone fleets, point-cloud capture software</t>
         </is>
       </c>
       <c r="M181" s="15" t="inlineStr">
@@ -15689,26 +15701,18 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N181" s="18" t="inlineStr">
-        <is>
-          <t>Hari Janarthanan</t>
-        </is>
-      </c>
-      <c r="O181" s="18" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="N181" s="18" t="inlineStr"/>
+      <c r="O181" s="18" t="inlineStr"/>
       <c r="P181" s="18" t="inlineStr"/>
       <c r="Q181" s="18" t="inlineStr"/>
       <c r="R181" s="18" t="inlineStr">
         <is>
-          <t>+91 82202 66060</t>
+          <t>+91 98402 81288</t>
         </is>
       </c>
       <c r="S181" s="17" t="inlineStr">
         <is>
-          <t>https://birdscale.com</t>
+          <t>https://ldrsurveys.com</t>
         </is>
       </c>
       <c r="T181" s="18" t="inlineStr"/>
@@ -15724,16 +15728,16 @@
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t>L D R Survey Pvt Ltd</t>
+          <t>Skywheelzs</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>https://ldrsurveys.com</t>
+          <t>https://skywheelzs.in</t>
         </is>
       </c>
       <c r="D182" s="11" t="n">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
@@ -15762,17 +15766,17 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>UAV/LiDAR land surveys; as-built site modeling</t>
+          <t>Commercial aerial imagery; live streaming drone operations</t>
         </is>
       </c>
       <c r="K182" s="14" t="inlineStr">
         <is>
-          <t>Sub-centimeter precision drone topographic mapping for legal and banking use</t>
+          <t>High-definition event broadcasting and infrastructure thermal imaging</t>
         </is>
       </c>
       <c r="L182" s="14" t="inlineStr">
         <is>
-          <t>DGCA-certified drone fleets, point-cloud capture software</t>
+          <t>DJI Matrice and Mavic enterprise systems, RTK high-precision sensors</t>
         </is>
       </c>
       <c r="M182" s="11" t="inlineStr">
@@ -15782,16 +15786,20 @@
       </c>
       <c r="N182" s="14" t="inlineStr"/>
       <c r="O182" s="14" t="inlineStr"/>
-      <c r="P182" s="14" t="inlineStr"/>
+      <c r="P182" s="13" t="inlineStr">
+        <is>
+          <t>hello@skywheelzs.in</t>
+        </is>
+      </c>
       <c r="Q182" s="14" t="inlineStr"/>
       <c r="R182" s="14" t="inlineStr">
         <is>
-          <t>+91 98402 81288</t>
+          <t>+91 93607 44915</t>
         </is>
       </c>
       <c r="S182" s="13" t="inlineStr">
         <is>
-          <t>https://ldrsurveys.com</t>
+          <t>https://skywheelzs.in</t>
         </is>
       </c>
       <c r="T182" s="14" t="inlineStr"/>
@@ -15807,16 +15815,16 @@
       </c>
       <c r="B183" s="16" t="inlineStr">
         <is>
-          <t>Skywheelzs</t>
+          <t>Aviatorq Drone Services</t>
         </is>
       </c>
       <c r="C183" s="17" t="inlineStr">
         <is>
-          <t>https://skywheelzs.in</t>
+          <t>https://aviatorq.in</t>
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
@@ -15845,17 +15853,17 @@
       </c>
       <c r="J183" s="18" t="inlineStr">
         <is>
-          <t>Commercial aerial imagery; live streaming drone operations</t>
+          <t>Drone fleet rentals; professional aerial training</t>
         </is>
       </c>
       <c r="K183" s="18" t="inlineStr">
         <is>
-          <t>High-definition event broadcasting and infrastructure thermal imaging</t>
+          <t>UAV systems application deployment and industrial mapping analysis</t>
         </is>
       </c>
       <c r="L183" s="18" t="inlineStr">
         <is>
-          <t>DJI Matrice and Mavic enterprise systems, RTK high-precision sensors</t>
+          <t>Custom flight control platforms, modular aerial surveying equipment</t>
         </is>
       </c>
       <c r="M183" s="15" t="inlineStr">
@@ -15867,18 +15875,18 @@
       <c r="O183" s="18" t="inlineStr"/>
       <c r="P183" s="17" t="inlineStr">
         <is>
-          <t>hello@skywheelzs.in</t>
+          <t>aviatorqdroneservices@gmail.com</t>
         </is>
       </c>
       <c r="Q183" s="18" t="inlineStr"/>
       <c r="R183" s="18" t="inlineStr">
         <is>
-          <t>+91 93607 44915</t>
+          <t>+91 73050 46689</t>
         </is>
       </c>
       <c r="S183" s="17" t="inlineStr">
         <is>
-          <t>https://skywheelzs.in</t>
+          <t>https://aviatorq.in</t>
         </is>
       </c>
       <c r="T183" s="18" t="inlineStr"/>
@@ -15888,22 +15896,22 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="33" customHeight="1">
+    <row r="184" ht="46.5" customHeight="1">
       <c r="A184" s="11" t="n">
         <v>179</v>
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>Aviatorq Drone Services</t>
+          <t>GNP Commercials</t>
         </is>
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>https://aviatorq.in</t>
+          <t>gnpc.in</t>
         </is>
       </c>
       <c r="D184" s="11" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
@@ -15927,45 +15935,37 @@
       </c>
       <c r="I184" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>Drone fleet rentals; professional aerial training</t>
+          <t>Wind turbine and solar plant aerial thermography; powerline infrastructure mapping; stockpile analysis</t>
         </is>
       </c>
       <c r="K184" s="14" t="inlineStr">
         <is>
-          <t>UAV systems application deployment and industrial mapping analysis</t>
+          <t>High-resolution 5.1K thermal radiometric drone imaging and asset health surveillance</t>
         </is>
       </c>
       <c r="L184" s="14" t="inlineStr">
         <is>
-          <t>Custom flight control platforms, modular aerial surveying equipment</t>
+          <t>Advanced radiometric thermal payloads, high-end optical zoom sensors</t>
         </is>
       </c>
       <c r="M184" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N184" s="14" t="inlineStr"/>
       <c r="O184" s="14" t="inlineStr"/>
-      <c r="P184" s="13" t="inlineStr">
-        <is>
-          <t>aviatorqdroneservices@gmail.com</t>
-        </is>
-      </c>
+      <c r="P184" s="14" t="inlineStr"/>
       <c r="Q184" s="14" t="inlineStr"/>
-      <c r="R184" s="14" t="inlineStr">
-        <is>
-          <t>+91 73050 46689</t>
-        </is>
-      </c>
+      <c r="R184" s="14" t="inlineStr"/>
       <c r="S184" s="13" t="inlineStr">
         <is>
-          <t>https://aviatorq.in</t>
+          <t>gnpc.in</t>
         </is>
       </c>
       <c r="T184" s="14" t="inlineStr"/>
@@ -15981,12 +15981,12 @@
       </c>
       <c r="B185" s="16" t="inlineStr">
         <is>
-          <t>GNP Commercials</t>
+          <t>Vayuratha Private Limited</t>
         </is>
       </c>
       <c r="C185" s="17" t="inlineStr">
         <is>
-          <t>gnpc.in</t>
+          <t>vayuratha.com</t>
         </is>
       </c>
       <c r="D185" s="15" t="n">
@@ -16014,27 +16014,27 @@
       </c>
       <c r="I185" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J185" s="18" t="inlineStr">
         <is>
-          <t>Wind turbine and solar plant aerial thermography; powerline infrastructure mapping; stockpile analysis</t>
+          <t>Agricultural drone spraying services; thermal solar farm inspections; remote pilot training</t>
         </is>
       </c>
       <c r="K185" s="18" t="inlineStr">
         <is>
-          <t>High-resolution 5.1K thermal radiometric drone imaging and asset health surveillance</t>
+          <t>Drone automation and crop-nutrient spraying applications backed by certified training workflows</t>
         </is>
       </c>
       <c r="L185" s="18" t="inlineStr">
         <is>
-          <t>Advanced radiometric thermal payloads, high-end optical zoom sensors</t>
+          <t>UAV aerial cinematographic tools, automated spraying systems, remote pilot simulation software</t>
         </is>
       </c>
       <c r="M185" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N185" s="18" t="inlineStr"/>
@@ -16044,7 +16044,7 @@
       <c r="R185" s="18" t="inlineStr"/>
       <c r="S185" s="17" t="inlineStr">
         <is>
-          <t>gnpc.in</t>
+          <t>vayuratha.com</t>
         </is>
       </c>
       <c r="T185" s="18" t="inlineStr"/>
@@ -16060,16 +16060,16 @@
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t>Vayuratha Private Limited</t>
+          <t>AstroX Aerospace Private Limited</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>vayuratha.com</t>
+          <t>astrox.co.in</t>
         </is>
       </c>
       <c r="D186" s="11" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
@@ -16098,17 +16098,17 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone spraying services; thermal solar farm inspections; remote pilot training</t>
+          <t>GIS drone mapping; cargo delivery services; industrial inspection services</t>
         </is>
       </c>
       <c r="K186" s="14" t="inlineStr">
         <is>
-          <t>Drone automation and crop-nutrient spraying applications backed by certified training workflows</t>
+          <t>5G and AI-enabled autonomous aerial system operations for logistics, defense, and surveying</t>
         </is>
       </c>
       <c r="L186" s="14" t="inlineStr">
         <is>
-          <t>UAV aerial cinematographic tools, automated spraying systems, remote pilot simulation software</t>
+          <t>AX-AI 5G Remote Link module, AstroX Cloud Intelligence platform</t>
         </is>
       </c>
       <c r="M186" s="11" t="inlineStr">
@@ -16123,7 +16123,7 @@
       <c r="R186" s="14" t="inlineStr"/>
       <c r="S186" s="13" t="inlineStr">
         <is>
-          <t>vayuratha.com</t>
+          <t>astrox.co.in</t>
         </is>
       </c>
       <c r="T186" s="14" t="inlineStr"/>
@@ -16139,16 +16139,16 @@
       </c>
       <c r="B187" s="16" t="inlineStr">
         <is>
-          <t>AstroX Aerospace Private Limited</t>
+          <t>Chennai Drone Academy</t>
         </is>
       </c>
       <c r="C187" s="17" t="inlineStr">
         <is>
-          <t>astrox.co.in</t>
+          <t>chennaidroneacademy.com</t>
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="E187" s="18" t="inlineStr">
         <is>
@@ -16172,22 +16172,22 @@
       </c>
       <c r="I187" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J187" s="18" t="inlineStr">
         <is>
-          <t>GIS drone mapping; cargo delivery services; industrial inspection services</t>
+          <t>Aerial cinematography services; drone mapping training; hardware maintenance and repairs</t>
         </is>
       </c>
       <c r="K187" s="18" t="inlineStr">
         <is>
-          <t>5G and AI-enabled autonomous aerial system operations for logistics, defense, and surveying</t>
+          <t>Comprehensive pilot rating certifications, tactical flight training, and aerial post-production filming</t>
         </is>
       </c>
       <c r="L187" s="18" t="inlineStr">
         <is>
-          <t>AX-AI 5G Remote Link module, AstroX Cloud Intelligence platform</t>
+          <t>DJI Mavic enterprise systems, FPV pilot gear setups</t>
         </is>
       </c>
       <c r="M187" s="15" t="inlineStr">
@@ -16202,7 +16202,7 @@
       <c r="R187" s="18" t="inlineStr"/>
       <c r="S187" s="17" t="inlineStr">
         <is>
-          <t>astrox.co.in</t>
+          <t>chennaidroneacademy.com</t>
         </is>
       </c>
       <c r="T187" s="18" t="inlineStr"/>
@@ -16218,20 +16218,20 @@
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t>Chennai Drone Academy</t>
+          <t>Level Tech</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>chennaidroneacademy.com</t>
+          <t>leveltech.in</t>
         </is>
       </c>
       <c r="D188" s="11" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F188" s="14" t="inlineStr">
@@ -16246,27 +16246,27 @@
       </c>
       <c r="H188" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I188" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>Aerial cinematography services; drone mapping training; hardware maintenance and repairs</t>
+          <t>Geospatial land documentation; precision layout surveying; infrastructure drone checking</t>
         </is>
       </c>
       <c r="K188" s="14" t="inlineStr">
         <is>
-          <t>Comprehensive pilot rating certifications, tactical flight training, and aerial post-production filming</t>
+          <t>High-precision digital mapping and professional drone site profiling solutions</t>
         </is>
       </c>
       <c r="L188" s="14" t="inlineStr">
         <is>
-          <t>DJI Mavic enterprise systems, FPV pilot gear setups</t>
+          <t>RTK/PPK drone mapping platforms, GNSS processing integration</t>
         </is>
       </c>
       <c r="M188" s="11" t="inlineStr">
@@ -16278,13 +16278,21 @@
       <c r="O188" s="14" t="inlineStr"/>
       <c r="P188" s="14" t="inlineStr"/>
       <c r="Q188" s="14" t="inlineStr"/>
-      <c r="R188" s="14" t="inlineStr"/>
+      <c r="R188" s="14" t="inlineStr">
+        <is>
+          <t>+91 99768 46909</t>
+        </is>
+      </c>
       <c r="S188" s="13" t="inlineStr">
         <is>
-          <t>chennaidroneacademy.com</t>
-        </is>
-      </c>
-      <c r="T188" s="14" t="inlineStr"/>
+          <t>leveltech.in</t>
+        </is>
+      </c>
+      <c r="T188" s="13" t="inlineStr">
+        <is>
+          <t>leveltech12@gmail.com</t>
+        </is>
+      </c>
       <c r="U188" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -16297,20 +16305,20 @@
       </c>
       <c r="B189" s="16" t="inlineStr">
         <is>
-          <t>Level Tech</t>
+          <t>GTG Geo Technical Solution</t>
         </is>
       </c>
       <c r="C189" s="17" t="inlineStr">
         <is>
-          <t>leveltech.in</t>
+          <t>gtggeo.com</t>
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E189" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F189" s="18" t="inlineStr">
@@ -16325,7 +16333,7 @@
       </c>
       <c r="H189" s="18" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I189" s="15" t="inlineStr">
@@ -16335,17 +16343,17 @@
       </c>
       <c r="J189" s="18" t="inlineStr">
         <is>
-          <t>Geospatial land documentation; precision layout surveying; infrastructure drone checking</t>
+          <t>Geotechnical subsurface surveying; drone aerial photography mapping; topographic verification</t>
         </is>
       </c>
       <c r="K189" s="18" t="inlineStr">
         <is>
-          <t>High-precision digital mapping and professional drone site profiling solutions</t>
+          <t>Engineering-grade site analysis and customized aerial terrain verification</t>
         </is>
       </c>
       <c r="L189" s="18" t="inlineStr">
         <is>
-          <t>RTK/PPK drone mapping platforms, GNSS processing integration</t>
+          <t>High-resolution photogrammetry drones, topographic spatial modeling software</t>
         </is>
       </c>
       <c r="M189" s="15" t="inlineStr">
@@ -16357,21 +16365,13 @@
       <c r="O189" s="18" t="inlineStr"/>
       <c r="P189" s="18" t="inlineStr"/>
       <c r="Q189" s="18" t="inlineStr"/>
-      <c r="R189" s="18" t="inlineStr">
-        <is>
-          <t>+91 99768 46909</t>
-        </is>
-      </c>
+      <c r="R189" s="18" t="inlineStr"/>
       <c r="S189" s="17" t="inlineStr">
         <is>
-          <t>leveltech.in</t>
-        </is>
-      </c>
-      <c r="T189" s="17" t="inlineStr">
-        <is>
-          <t>leveltech12@gmail.com</t>
-        </is>
-      </c>
+          <t>gtggeo.com</t>
+        </is>
+      </c>
+      <c r="T189" s="18" t="inlineStr"/>
       <c r="U189" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -16384,20 +16384,20 @@
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t>GTG Geo Technical Solution</t>
+          <t>Kongunadu Surveyor</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>gtggeo.com</t>
+          <t>kongunadusurveyor.in</t>
         </is>
       </c>
       <c r="D190" s="11" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F190" s="14" t="inlineStr">
@@ -16412,45 +16412,61 @@
       </c>
       <c r="H190" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I190" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>Geotechnical subsurface surveying; drone aerial photography mapping; topographic verification</t>
+          <t>Topographic mapping charts; digital terrain models; earthwork volume computations</t>
         </is>
       </c>
       <c r="K190" s="14" t="inlineStr">
         <is>
-          <t>Engineering-grade site analysis and customized aerial terrain verification</t>
+          <t>Digital infrastructure surveys and highway alignment planning analytics</t>
         </is>
       </c>
       <c r="L190" s="14" t="inlineStr">
         <is>
-          <t>High-resolution photogrammetry drones, topographic spatial modeling software</t>
+          <t>Aerial photogrammetry; Total Station; digital terrain modeling software</t>
         </is>
       </c>
       <c r="M190" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N190" s="14" t="inlineStr"/>
-      <c r="O190" s="14" t="inlineStr"/>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N190" s="14" t="inlineStr">
+        <is>
+          <t>Arunmaharaja</t>
+        </is>
+      </c>
+      <c r="O190" s="14" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="P190" s="14" t="inlineStr"/>
       <c r="Q190" s="14" t="inlineStr"/>
-      <c r="R190" s="14" t="inlineStr"/>
+      <c r="R190" s="14" t="inlineStr">
+        <is>
+          <t>+91 90036 63323</t>
+        </is>
+      </c>
       <c r="S190" s="13" t="inlineStr">
         <is>
-          <t>gtggeo.com</t>
-        </is>
-      </c>
-      <c r="T190" s="14" t="inlineStr"/>
+          <t>kongunadusurveyor.in</t>
+        </is>
+      </c>
+      <c r="T190" s="13" t="inlineStr">
+        <is>
+          <t>info@kongunadusurveyor.in</t>
+        </is>
+      </c>
       <c r="U190" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -16463,20 +16479,20 @@
       </c>
       <c r="B191" s="16" t="inlineStr">
         <is>
-          <t>Kongunadu Surveyor</t>
+          <t>Aero2Astro</t>
         </is>
       </c>
       <c r="C191" s="17" t="inlineStr">
         <is>
-          <t>kongunadusurveyor.in</t>
+          <t>aero2astro.com</t>
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="E191" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F191" s="18" t="inlineStr">
@@ -16491,83 +16507,75 @@
       </c>
       <c r="H191" s="18" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I191" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J191" s="18" t="inlineStr">
         <is>
-          <t>Topographic mapping charts; digital terrain models; earthwork volume computations</t>
+          <t>Digital twins datasets; wind turbine inspection reports; solar thermal hotspot data</t>
         </is>
       </c>
       <c r="K191" s="18" t="inlineStr">
         <is>
-          <t>Digital infrastructure surveys and highway alignment planning analytics</t>
+          <t>Industrial infrastructure asset performance and geospatial intelligence analytics</t>
         </is>
       </c>
       <c r="L191" s="18" t="inlineStr">
         <is>
-          <t>Aerial photogrammetry; Total Station; digital terrain modeling software</t>
+          <t>AI thermal analytics; 3D oblique mapping; compliance management automation tools</t>
         </is>
       </c>
       <c r="M191" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N191" s="18" t="inlineStr">
         <is>
-          <t>Arunmaharaja</t>
+          <t>Ted Solomon</t>
         </is>
       </c>
       <c r="O191" s="18" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="P191" s="18" t="inlineStr"/>
       <c r="Q191" s="18" t="inlineStr"/>
-      <c r="R191" s="18" t="inlineStr">
-        <is>
-          <t>+91 90036 63323</t>
-        </is>
-      </c>
+      <c r="R191" s="18" t="inlineStr"/>
       <c r="S191" s="17" t="inlineStr">
         <is>
-          <t>kongunadusurveyor.in</t>
-        </is>
-      </c>
-      <c r="T191" s="17" t="inlineStr">
-        <is>
-          <t>info@kongunadusurveyor.in</t>
-        </is>
-      </c>
+          <t>aero2astro.com</t>
+        </is>
+      </c>
+      <c r="T191" s="18" t="inlineStr"/>
       <c r="U191" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="46.5" customHeight="1">
+    <row r="192" ht="33" customHeight="1">
       <c r="A192" s="11" t="n">
         <v>187</v>
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t>Aero2Astro</t>
+          <t>Chennai FPV Drones</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>aero2astro.com</t>
+          <t>chennaifpvdrones.in</t>
         </is>
       </c>
       <c r="D192" s="11" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
@@ -16596,17 +16604,17 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>Digital twins datasets; wind turbine inspection reports; solar thermal hotspot data</t>
+          <t>FPV cinematography; industrial drone inspections; land mapping</t>
         </is>
       </c>
       <c r="K192" s="14" t="inlineStr">
         <is>
-          <t>Industrial infrastructure asset performance and geospatial intelligence analytics</t>
+          <t>Immersive FPV event capture and industrial plant shutdown checks</t>
         </is>
       </c>
       <c r="L192" s="14" t="inlineStr">
         <is>
-          <t>AI thermal analytics; 3D oblique mapping; compliance management automation tools</t>
+          <t>First-Person View (FPV) imaging; survey-grade land mapping analytics</t>
         </is>
       </c>
       <c r="M192" s="11" t="inlineStr">
@@ -16614,22 +16622,14 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N192" s="14" t="inlineStr">
-        <is>
-          <t>Ted Solomon</t>
-        </is>
-      </c>
-      <c r="O192" s="14" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
+      <c r="N192" s="14" t="inlineStr"/>
+      <c r="O192" s="14" t="inlineStr"/>
       <c r="P192" s="14" t="inlineStr"/>
       <c r="Q192" s="14" t="inlineStr"/>
       <c r="R192" s="14" t="inlineStr"/>
       <c r="S192" s="13" t="inlineStr">
         <is>
-          <t>aero2astro.com</t>
+          <t>chennaifpvdrones.in</t>
         </is>
       </c>
       <c r="T192" s="14" t="inlineStr"/>
@@ -16645,20 +16645,20 @@
       </c>
       <c r="B193" s="16" t="inlineStr">
         <is>
-          <t>Chennai FPV Drones</t>
+          <t>Aerial Drobotics Private Limited</t>
         </is>
       </c>
       <c r="C193" s="17" t="inlineStr">
         <is>
-          <t>chennaifpvdrones.in</t>
+          <t>aerialdrobotics.com</t>
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E193" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Namakkal, India</t>
         </is>
       </c>
       <c r="F193" s="18" t="inlineStr">
@@ -16678,22 +16678,22 @@
       </c>
       <c r="I193" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J193" s="18" t="inlineStr">
         <is>
-          <t>FPV cinematography; industrial drone inspections; land mapping</t>
+          <t>Agriculture drone operations; mapping services</t>
         </is>
       </c>
       <c r="K193" s="18" t="inlineStr">
         <is>
-          <t>Immersive FPV event capture and industrial plant shutdown checks</t>
+          <t>Precision aerial spraying and topographic farm monitoring</t>
         </is>
       </c>
       <c r="L193" s="18" t="inlineStr">
         <is>
-          <t>First-Person View (FPV) imaging; survey-grade land mapping analytics</t>
+          <t>Autonomous flight seed spraying; agricultural mapping software datasets</t>
         </is>
       </c>
       <c r="M193" s="15" t="inlineStr">
@@ -16708,7 +16708,7 @@
       <c r="R193" s="18" t="inlineStr"/>
       <c r="S193" s="17" t="inlineStr">
         <is>
-          <t>chennaifpvdrones.in</t>
+          <t>aerialdrobotics.com</t>
         </is>
       </c>
       <c r="T193" s="18" t="inlineStr"/>
@@ -16718,18 +16718,18 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="33" customHeight="1">
+    <row r="194" ht="46.5" customHeight="1">
       <c r="A194" s="11" t="n">
         <v>189</v>
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t>Aerial Drobotics Private Limited</t>
+          <t>SSIG Geospatial World Private Limited</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>aerialdrobotics.com</t>
+          <t>https://ssiggeospatial.com</t>
         </is>
       </c>
       <c r="D194" s="11" t="n">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>Namakkal, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F194" s="14" t="inlineStr">
@@ -16762,17 +16762,17 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>Agriculture drone operations; mapping services</t>
+          <t>UAV drone surveying services; digital photogrammetry; GIS mapping services</t>
         </is>
       </c>
       <c r="K194" s="14" t="inlineStr">
         <is>
-          <t>Precision aerial spraying and topographic farm monitoring</t>
+          <t>Geospatial solutions and advanced remote sensing data management using unmanned aerial vehicles.</t>
         </is>
       </c>
       <c r="L194" s="14" t="inlineStr">
         <is>
-          <t>Autonomous flight seed spraying; agricultural mapping software datasets</t>
+          <t>UAV drone data acquisition; digital photogrammetry; LiDAR mapping; DGPS surveys</t>
         </is>
       </c>
       <c r="M194" s="11" t="inlineStr">
@@ -16784,35 +16784,43 @@
       <c r="O194" s="14" t="inlineStr"/>
       <c r="P194" s="14" t="inlineStr"/>
       <c r="Q194" s="14" t="inlineStr"/>
-      <c r="R194" s="14" t="inlineStr"/>
+      <c r="R194" s="14" t="inlineStr">
+        <is>
+          <t>+91 7845174301</t>
+        </is>
+      </c>
       <c r="S194" s="13" t="inlineStr">
         <is>
-          <t>aerialdrobotics.com</t>
-        </is>
-      </c>
-      <c r="T194" s="14" t="inlineStr"/>
+          <t>https://ssiggeospatial.com</t>
+        </is>
+      </c>
+      <c r="T194" s="13" t="inlineStr">
+        <is>
+          <t>info@ssiggeospatial.com</t>
+        </is>
+      </c>
       <c r="U194" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="46.5" customHeight="1">
+    <row r="195" ht="33" customHeight="1">
       <c r="A195" s="15" t="n">
         <v>190</v>
       </c>
       <c r="B195" s="16" t="inlineStr">
         <is>
-          <t>SSIG Geospatial World Private Limited</t>
+          <t>WhiteOx Private Limited</t>
         </is>
       </c>
       <c r="C195" s="17" t="inlineStr">
         <is>
-          <t>https://ssiggeospatial.com</t>
+          <t>whiteox.in</t>
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E195" s="18" t="inlineStr">
         <is>
@@ -16836,22 +16844,22 @@
       </c>
       <c r="I195" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J195" s="18" t="inlineStr">
         <is>
-          <t>UAV drone surveying services; digital photogrammetry; GIS mapping services</t>
+          <t>Agricultural drone services; Precision spraying operations</t>
         </is>
       </c>
       <c r="K195" s="18" t="inlineStr">
         <is>
-          <t>Geospatial solutions and advanced remote sensing data management using unmanned aerial vehicles.</t>
+          <t>Resource-efficient pesticide and fertilizer drone application</t>
         </is>
       </c>
       <c r="L195" s="18" t="inlineStr">
         <is>
-          <t>UAV drone data acquisition; digital photogrammetry; LiDAR mapping; DGPS surveys</t>
+          <t>Liquid-spraying agricultural drone platforms</t>
         </is>
       </c>
       <c r="M195" s="15" t="inlineStr">
@@ -16861,21 +16869,25 @@
       </c>
       <c r="N195" s="18" t="inlineStr"/>
       <c r="O195" s="18" t="inlineStr"/>
-      <c r="P195" s="18" t="inlineStr"/>
+      <c r="P195" s="17" t="inlineStr">
+        <is>
+          <t>support@whiteox.in</t>
+        </is>
+      </c>
       <c r="Q195" s="18" t="inlineStr"/>
       <c r="R195" s="18" t="inlineStr">
         <is>
-          <t>+91 7845174301</t>
+          <t>+91 81110 15577</t>
         </is>
       </c>
       <c r="S195" s="17" t="inlineStr">
         <is>
-          <t>https://ssiggeospatial.com</t>
+          <t>whiteox.in</t>
         </is>
       </c>
       <c r="T195" s="17" t="inlineStr">
         <is>
-          <t>info@ssiggeospatial.com</t>
+          <t>support@whiteox.in</t>
         </is>
       </c>
       <c r="U195" s="15" t="inlineStr">
@@ -16890,16 +16902,16 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t>WhiteOx Private Limited</t>
+          <t>Skyrider Aerosolutions Chennai</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>whiteox.in</t>
+          <t>skyrideraerosolutions.com</t>
         </is>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
@@ -16928,47 +16940,39 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone services; Precision spraying operations</t>
+          <t>Drone assembly training; Aeromodelling instructional workshops</t>
         </is>
       </c>
       <c r="K196" s="14" t="inlineStr">
         <is>
-          <t>Resource-efficient pesticide and fertilizer drone application</t>
+          <t>Practical remote control flight instruction and drone fabrication pedagogy</t>
         </is>
       </c>
       <c r="L196" s="14" t="inlineStr">
         <is>
-          <t>Liquid-spraying agricultural drone platforms</t>
+          <t>Unmanned aerial vehicle assembly kits</t>
         </is>
       </c>
       <c r="M196" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N196" s="14" t="inlineStr"/>
       <c r="O196" s="14" t="inlineStr"/>
-      <c r="P196" s="13" t="inlineStr">
-        <is>
-          <t>support@whiteox.in</t>
-        </is>
-      </c>
+      <c r="P196" s="14" t="inlineStr"/>
       <c r="Q196" s="14" t="inlineStr"/>
       <c r="R196" s="14" t="inlineStr">
         <is>
-          <t>+91 81110 15577</t>
+          <t>+91 95000 98051</t>
         </is>
       </c>
       <c r="S196" s="13" t="inlineStr">
         <is>
-          <t>whiteox.in</t>
-        </is>
-      </c>
-      <c r="T196" s="13" t="inlineStr">
-        <is>
-          <t>support@whiteox.in</t>
-        </is>
-      </c>
+          <t>skyrideraerosolutions.com</t>
+        </is>
+      </c>
+      <c r="T196" s="14" t="inlineStr"/>
       <c r="U196" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -16981,12 +16985,12 @@
       </c>
       <c r="B197" s="16" t="inlineStr">
         <is>
-          <t>Skyrider Aerosolutions Chennai</t>
+          <t>Drone Hub Nxt</t>
         </is>
       </c>
       <c r="C197" s="17" t="inlineStr">
         <is>
-          <t>skyrideraerosolutions.com</t>
+          <t>dronehubnxt.com</t>
         </is>
       </c>
       <c r="D197" s="15" t="n">
@@ -17014,41 +17018,37 @@
       </c>
       <c r="I197" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J197" s="18" t="inlineStr">
         <is>
-          <t>Drone assembly training; Aeromodelling instructional workshops</t>
+          <t>Land geotagging; 2D orthomosaic mapping; construction progress monitoring</t>
         </is>
       </c>
       <c r="K197" s="18" t="inlineStr">
         <is>
-          <t>Practical remote control flight instruction and drone fabrication pedagogy</t>
+          <t>High-precision aerial triangulation and construction site topographic mapping</t>
         </is>
       </c>
       <c r="L197" s="18" t="inlineStr">
         <is>
-          <t>Unmanned aerial vehicle assembly kits</t>
+          <t>DGPS integrated drone mapping; aerial photogrammetry; orthomosaic generation</t>
         </is>
       </c>
       <c r="M197" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N197" s="18" t="inlineStr"/>
       <c r="O197" s="18" t="inlineStr"/>
       <c r="P197" s="18" t="inlineStr"/>
       <c r="Q197" s="18" t="inlineStr"/>
-      <c r="R197" s="18" t="inlineStr">
-        <is>
-          <t>+91 95000 98051</t>
-        </is>
-      </c>
+      <c r="R197" s="18" t="inlineStr"/>
       <c r="S197" s="17" t="inlineStr">
         <is>
-          <t>skyrideraerosolutions.com</t>
+          <t>dronehubnxt.com</t>
         </is>
       </c>
       <c r="T197" s="18" t="inlineStr"/>
@@ -17064,16 +17064,16 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t>Drone Hub Nxt</t>
+          <t>Aeroline Topomappers</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
         <is>
-          <t>dronehubnxt.com</t>
+          <t>aerolinetopomappers.com</t>
         </is>
       </c>
       <c r="D198" s="11" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
@@ -17097,22 +17097,22 @@
       </c>
       <c r="I198" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>Land geotagging; 2D orthomosaic mapping; construction progress monitoring</t>
+          <t>Topographic drone mapping; route alignment surveying; cadastral drone mapping</t>
         </is>
       </c>
       <c r="K198" s="14" t="inlineStr">
         <is>
-          <t>High-precision aerial triangulation and construction site topographic mapping</t>
+          <t>Corridor mapping for highways and railways using unmanned aerial systems</t>
         </is>
       </c>
       <c r="L198" s="14" t="inlineStr">
         <is>
-          <t>DGPS integrated drone mapping; aerial photogrammetry; orthomosaic generation</t>
+          <t>Drone photogrammetry; contours and DEM generation; high-resolution orthophotos</t>
         </is>
       </c>
       <c r="M198" s="11" t="inlineStr">
@@ -17127,7 +17127,7 @@
       <c r="R198" s="14" t="inlineStr"/>
       <c r="S198" s="13" t="inlineStr">
         <is>
-          <t>dronehubnxt.com</t>
+          <t>aerolinetopomappers.com</t>
         </is>
       </c>
       <c r="T198" s="14" t="inlineStr"/>
@@ -17137,26 +17137,26 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="33" customHeight="1">
+    <row r="199" ht="46.5" customHeight="1">
       <c r="A199" s="15" t="n">
         <v>194</v>
       </c>
       <c r="B199" s="16" t="inlineStr">
         <is>
-          <t>Aeroline Topomappers</t>
+          <t>Indiza Aviation</t>
         </is>
       </c>
       <c r="C199" s="17" t="inlineStr">
         <is>
-          <t>aerolinetopomappers.com</t>
+          <t>indizaaviation.in</t>
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="E199" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F199" s="18" t="inlineStr">
@@ -17176,22 +17176,22 @@
       </c>
       <c r="I199" s="15" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J199" s="18" t="inlineStr">
         <is>
-          <t>Topographic drone mapping; route alignment surveying; cadastral drone mapping</t>
+          <t>Certified pilot training; precision agriculture spraying; forest volume mapping</t>
         </is>
       </c>
       <c r="K199" s="18" t="inlineStr">
         <is>
-          <t>Corridor mapping for highways and railways using unmanned aerial systems</t>
+          <t>Regulated aviation training workflows and custom deployment of high-payload agricultural flights</t>
         </is>
       </c>
       <c r="L199" s="18" t="inlineStr">
         <is>
-          <t>Drone photogrammetry; contours and DEM generation; high-resolution orthophotos</t>
+          <t>NDVI crop scanning sensors; custom heavy-payload carbon-fiber systems</t>
         </is>
       </c>
       <c r="M199" s="15" t="inlineStr">
@@ -17206,7 +17206,7 @@
       <c r="R199" s="18" t="inlineStr"/>
       <c r="S199" s="17" t="inlineStr">
         <is>
-          <t>aerolinetopomappers.com</t>
+          <t>indizaaviation.in</t>
         </is>
       </c>
       <c r="T199" s="18" t="inlineStr"/>
@@ -17222,20 +17222,20 @@
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t>Indiza Aviation</t>
+          <t>Gridline Surveys and Geospatial Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>indizaaviation.in</t>
+          <t>gridlinesurveys.com</t>
         </is>
       </c>
       <c r="D200" s="11" t="n">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F200" s="14" t="inlineStr">
@@ -17255,40 +17255,52 @@
       </c>
       <c r="I200" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>201-500</t>
         </is>
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>Certified pilot training; precision agriculture spraying; forest volume mapping</t>
+          <t>UAV drone topographic surveying; corridor alignment mapping; volumetric analysis for open-cast mines</t>
         </is>
       </c>
       <c r="K200" s="14" t="inlineStr">
         <is>
-          <t>Regulated aviation training workflows and custom deployment of high-payload agricultural flights</t>
+          <t>High-precision geodetic control networks and advanced mobile mapping for large civil infrastructure projects</t>
         </is>
       </c>
       <c r="L200" s="14" t="inlineStr">
         <is>
-          <t>NDVI crop scanning sensors; custom heavy-payload carbon-fiber systems</t>
+          <t>Aerial LiDAR scanners, DGCA-approved mapping drones, RTK-GPS receivers, and Total Station tracking hardware</t>
         </is>
       </c>
       <c r="M200" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N200" s="14" t="inlineStr"/>
       <c r="O200" s="14" t="inlineStr"/>
-      <c r="P200" s="14" t="inlineStr"/>
+      <c r="P200" s="13" t="inlineStr">
+        <is>
+          <t>gsagpl@gmail.com</t>
+        </is>
+      </c>
       <c r="Q200" s="14" t="inlineStr"/>
-      <c r="R200" s="14" t="inlineStr"/>
+      <c r="R200" s="14" t="inlineStr">
+        <is>
+          <t>+919994814720</t>
+        </is>
+      </c>
       <c r="S200" s="13" t="inlineStr">
         <is>
-          <t>indizaaviation.in</t>
-        </is>
-      </c>
-      <c r="T200" s="14" t="inlineStr"/>
+          <t>gridlinesurveys.com</t>
+        </is>
+      </c>
+      <c r="T200" s="13" t="inlineStr">
+        <is>
+          <t>gsagpl@gmail.com</t>
+        </is>
+      </c>
       <c r="U200" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -17301,16 +17313,16 @@
       </c>
       <c r="B201" s="16" t="inlineStr">
         <is>
-          <t>Gridline Surveys and Geospatial Pvt. Ltd.</t>
+          <t>Velciti Consulting Engineers Private Limited</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>gridlinesurveys.com</t>
+          <t>velciti.com</t>
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E201" s="18" t="inlineStr">
         <is>
@@ -17334,22 +17346,22 @@
       </c>
       <c r="I201" s="15" t="inlineStr">
         <is>
-          <t>201-500</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="J201" s="18" t="inlineStr">
         <is>
-          <t>UAV drone topographic surveying; corridor alignment mapping; volumetric analysis for open-cast mines</t>
+          <t>Drone photogrammetry; geotechnical investigation; infrastructure asset mapping; GIS spatial analysis</t>
         </is>
       </c>
       <c r="K201" s="18" t="inlineStr">
         <is>
-          <t>High-precision geodetic control networks and advanced mobile mapping for large civil infrastructure projects</t>
+          <t>Blending drone-derived geodetic models with subsurface geotechnical engineering insights for national highways</t>
         </is>
       </c>
       <c r="L201" s="18" t="inlineStr">
         <is>
-          <t>Aerial LiDAR scanners, DGCA-approved mapping drones, RTK-GPS receivers, and Total Station tracking hardware</t>
+          <t>UAV mapping platforms, high-resolution RGB cameras, LiDAR sensors, DGPS units, and ArcGIS processing tools</t>
         </is>
       </c>
       <c r="M201" s="15" t="inlineStr">
@@ -17357,27 +17369,31 @@
           <t>Offline</t>
         </is>
       </c>
-      <c r="N201" s="18" t="inlineStr"/>
-      <c r="O201" s="18" t="inlineStr"/>
-      <c r="P201" s="17" t="inlineStr">
-        <is>
-          <t>gsagpl@gmail.com</t>
-        </is>
-      </c>
+      <c r="N201" s="18" t="inlineStr">
+        <is>
+          <t>Satheesh Gopi</t>
+        </is>
+      </c>
+      <c r="O201" s="18" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="P201" s="18" t="inlineStr"/>
       <c r="Q201" s="18" t="inlineStr"/>
       <c r="R201" s="18" t="inlineStr">
         <is>
-          <t>+919994814720</t>
+          <t>+919384033283</t>
         </is>
       </c>
       <c r="S201" s="17" t="inlineStr">
         <is>
-          <t>gridlinesurveys.com</t>
+          <t>velciti.com</t>
         </is>
       </c>
       <c r="T201" s="17" t="inlineStr">
         <is>
-          <t>gsagpl@gmail.com</t>
+          <t>marketing.velciti@gmail.com</t>
         </is>
       </c>
       <c r="U201" s="15" t="inlineStr">
@@ -17392,20 +17408,20 @@
       </c>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t>Velciti Consulting Engineers Private Limited</t>
+          <t>Aerdroids Technology Private Limited</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>velciti.com</t>
+          <t>aerdroids.com</t>
         </is>
       </c>
       <c r="D202" s="11" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F202" s="14" t="inlineStr">
@@ -17425,56 +17441,48 @@
       </c>
       <c r="I202" s="11" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>Drone photogrammetry; geotechnical investigation; infrastructure asset mapping; GIS spatial analysis</t>
+          <t>Remote pilot training; commercial drone aviation certifications; aerial cinematography</t>
         </is>
       </c>
       <c r="K202" s="14" t="inlineStr">
         <is>
-          <t>Blending drone-derived geodetic models with subsurface geotechnical engineering insights for national highways</t>
+          <t>DGCA-compliant flight training operations paired with regional agricultural and wedding drone operations</t>
         </is>
       </c>
       <c r="L202" s="14" t="inlineStr">
         <is>
-          <t>UAV mapping platforms, high-resolution RGB cameras, LiDAR sensors, DGPS units, and ArcGIS processing tools</t>
+          <t>DGCA type-certified agricultural quadcopters, specialized remote pilot training flight simulators, and DJI cinematic cameras</t>
         </is>
       </c>
       <c r="M202" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N202" s="14" t="inlineStr">
         <is>
-          <t>Satheesh Gopi</t>
+          <t>Suresh Narayanan Muthukrishnan</t>
         </is>
       </c>
       <c r="O202" s="14" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Founder and Director</t>
         </is>
       </c>
       <c r="P202" s="14" t="inlineStr"/>
       <c r="Q202" s="14" t="inlineStr"/>
-      <c r="R202" s="14" t="inlineStr">
-        <is>
-          <t>+919384033283</t>
-        </is>
-      </c>
+      <c r="R202" s="14" t="inlineStr"/>
       <c r="S202" s="13" t="inlineStr">
         <is>
-          <t>velciti.com</t>
-        </is>
-      </c>
-      <c r="T202" s="13" t="inlineStr">
-        <is>
-          <t>marketing.velciti@gmail.com</t>
-        </is>
-      </c>
+          <t>aerdroids.com</t>
+        </is>
+      </c>
+      <c r="T202" s="14" t="inlineStr"/>
       <c r="U202" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -17487,30 +17495,30 @@
       </c>
       <c r="B203" s="16" t="inlineStr">
         <is>
-          <t>Aerdroids Technology Private Limited</t>
+          <t>A-Star Testing &amp; Inspection Private Limited</t>
         </is>
       </c>
       <c r="C203" s="17" t="inlineStr">
         <is>
-          <t>aerdroids.com</t>
+          <t>astartesting.co.in</t>
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="E203" s="18" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F203" s="18" t="inlineStr">
         <is>
-          <t>APAC(India)</t>
+          <t>APAC(India, Singapore, Malaysia)</t>
         </is>
       </c>
       <c r="G203" s="18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; Singapore; Malaysia; Indonesia</t>
         </is>
       </c>
       <c r="H203" s="18" t="inlineStr">
@@ -17520,51 +17528,43 @@
       </c>
       <c r="I203" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>100-500</t>
         </is>
       </c>
       <c r="J203" s="18" t="inlineStr">
         <is>
-          <t>Remote pilot training; commercial drone aviation certifications; aerial cinematography</t>
+          <t>UAV visual inspections; non-destructive testing (NDT); offshore marine structure monitoring</t>
         </is>
       </c>
       <c r="K203" s="18" t="inlineStr">
         <is>
-          <t>DGCA-compliant flight training operations paired with regional agricultural and wedding drone operations</t>
+          <t>Combining aerial drone imaging with specialized marine, oil and gas, and refinery asset integrity monitoring</t>
         </is>
       </c>
       <c r="L203" s="18" t="inlineStr">
         <is>
-          <t>DGCA type-certified agricultural quadcopters, specialized remote pilot training flight simulators, and DJI cinematic cameras</t>
+          <t>High-resolution optical zoom drone systems, thermal infrared cameras, and non-destructive testing tracking instruments</t>
         </is>
       </c>
       <c r="M203" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N203" s="18" t="inlineStr">
-        <is>
-          <t>Suresh Narayanan Muthukrishnan</t>
-        </is>
-      </c>
-      <c r="O203" s="18" t="inlineStr">
-        <is>
-          <t>Founder and Director</t>
-        </is>
-      </c>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N203" s="18" t="inlineStr"/>
+      <c r="O203" s="18" t="inlineStr"/>
       <c r="P203" s="18" t="inlineStr"/>
       <c r="Q203" s="18" t="inlineStr"/>
       <c r="R203" s="18" t="inlineStr"/>
       <c r="S203" s="17" t="inlineStr">
         <is>
-          <t>aerdroids.com</t>
+          <t>astartesting.co.in</t>
         </is>
       </c>
       <c r="T203" s="18" t="inlineStr"/>
       <c r="U203" s="15" t="inlineStr">
         <is>
-          <t>+91 / IN</t>
+          <t>+91 / IN; +65 / SG; +60 / MY</t>
         </is>
       </c>
     </row>
@@ -17574,16 +17574,16 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t>A-Star Testing &amp; Inspection Private Limited</t>
+          <t>NEST NDT Services</t>
         </is>
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>astartesting.co.in</t>
+          <t>nestndtservices.in</t>
         </is>
       </c>
       <c r="D204" s="11" t="n">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="E204" s="14" t="inlineStr">
         <is>
@@ -17592,12 +17592,12 @@
       </c>
       <c r="F204" s="14" t="inlineStr">
         <is>
-          <t>APAC(India, Singapore, Malaysia)</t>
+          <t>APAC(India)</t>
         </is>
       </c>
       <c r="G204" s="14" t="inlineStr">
         <is>
-          <t>India; Singapore; Malaysia; Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr">
@@ -17607,22 +17607,22 @@
       </c>
       <c r="I204" s="11" t="inlineStr">
         <is>
-          <t>100-500</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>UAV visual inspections; non-destructive testing (NDT); offshore marine structure monitoring</t>
+          <t>Confined space drone monitoring; industrial non-destructive engineering inspections; technical asset evaluation</t>
         </is>
       </c>
       <c r="K204" s="14" t="inlineStr">
         <is>
-          <t>Combining aerial drone imaging with specialized marine, oil and gas, and refinery asset integrity monitoring</t>
+          <t>In-line pipeline tracking and internal cage-enclosed drone inspections for hazardous factory environments</t>
         </is>
       </c>
       <c r="L204" s="14" t="inlineStr">
         <is>
-          <t>High-resolution optical zoom drone systems, thermal infrared cameras, and non-destructive testing tracking instruments</t>
+          <t>Cage-protected inspection drones, radiometric cameras, specialized internal lighting instruments, and robotic crawlers</t>
         </is>
       </c>
       <c r="M204" s="11" t="inlineStr">
@@ -17637,13 +17637,13 @@
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="13" t="inlineStr">
         <is>
-          <t>astartesting.co.in</t>
+          <t>nestndtservices.in</t>
         </is>
       </c>
       <c r="T204" s="14" t="inlineStr"/>
       <c r="U204" s="11" t="inlineStr">
         <is>
-          <t>+91 / IN; +65 / SG; +60 / MY</t>
+          <t>+91 / IN</t>
         </is>
       </c>
     </row>
@@ -17653,16 +17653,16 @@
       </c>
       <c r="B205" s="16" t="inlineStr">
         <is>
-          <t>NEST NDT Services</t>
+          <t>Bennysurya Venture Private Limited</t>
         </is>
       </c>
       <c r="C205" s="17" t="inlineStr">
         <is>
-          <t>nestndtservices.in</t>
+          <t>https://bennysurya.com</t>
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="E205" s="18" t="inlineStr">
         <is>
@@ -17686,22 +17686,22 @@
       </c>
       <c r="I205" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>20-100</t>
         </is>
       </c>
       <c r="J205" s="18" t="inlineStr">
         <is>
-          <t>Confined space drone monitoring; industrial non-destructive engineering inspections; technical asset evaluation</t>
+          <t>Confined space drone inspection; Industrial surface defect mapping; Aerial asset NDT support</t>
         </is>
       </c>
       <c r="K205" s="18" t="inlineStr">
         <is>
-          <t>In-line pipeline tracking and internal cage-enclosed drone inspections for hazardous factory environments</t>
+          <t>On-site commercial asset defect detection in dangerous or hard-to-access chemical and engineering industrial plants.</t>
         </is>
       </c>
       <c r="L205" s="18" t="inlineStr">
         <is>
-          <t>Cage-protected inspection drones, radiometric cameras, specialized internal lighting instruments, and robotic crawlers</t>
+          <t>ASNT Level II certified assessment workflows, specialized inspection drone instrumentation.</t>
         </is>
       </c>
       <c r="M205" s="15" t="inlineStr">
@@ -17716,7 +17716,7 @@
       <c r="R205" s="18" t="inlineStr"/>
       <c r="S205" s="17" t="inlineStr">
         <is>
-          <t>nestndtservices.in</t>
+          <t>https://bennysurya.com</t>
         </is>
       </c>
       <c r="T205" s="18" t="inlineStr"/>
@@ -17726,22 +17726,22 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="46.5" customHeight="1">
+    <row r="206" ht="33" customHeight="1">
       <c r="A206" s="11" t="n">
         <v>201</v>
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t>Bennysurya Venture Private Limited</t>
+          <t>Maavan Drone Academy</t>
         </is>
       </c>
       <c r="C206" s="13" t="inlineStr">
         <is>
-          <t>https://bennysurya.com</t>
+          <t>maavandrones.com</t>
         </is>
       </c>
       <c r="D206" s="11" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
@@ -17765,27 +17765,27 @@
       </c>
       <c r="I206" s="11" t="inlineStr">
         <is>
-          <t>20-100</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>Confined space drone inspection; Industrial surface defect mapping; Aerial asset NDT support</t>
+          <t>UAV flight training; drone assembly courses</t>
         </is>
       </c>
       <c r="K206" s="14" t="inlineStr">
         <is>
-          <t>On-site commercial asset defect detection in dangerous or hard-to-access chemical and engineering industrial plants.</t>
+          <t>Drone design and pilot simulation training</t>
         </is>
       </c>
       <c r="L206" s="14" t="inlineStr">
         <is>
-          <t>ASNT Level II certified assessment workflows, specialized inspection drone instrumentation.</t>
+          <t>Fixed-wing piloting; autopilot programming</t>
         </is>
       </c>
       <c r="M206" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N206" s="14" t="inlineStr"/>
@@ -17795,7 +17795,7 @@
       <c r="R206" s="14" t="inlineStr"/>
       <c r="S206" s="13" t="inlineStr">
         <is>
-          <t>https://bennysurya.com</t>
+          <t>maavandrones.com</t>
         </is>
       </c>
       <c r="T206" s="14" t="inlineStr"/>
@@ -17811,20 +17811,20 @@
       </c>
       <c r="B207" s="16" t="inlineStr">
         <is>
-          <t>Maavan Drone Academy</t>
+          <t>Aerotics Technologies LLP</t>
         </is>
       </c>
       <c r="C207" s="17" t="inlineStr">
         <is>
-          <t>maavandrones.com</t>
+          <t>aeroticstechnologies.com</t>
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="E207" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F207" s="18" t="inlineStr">
@@ -17844,22 +17844,22 @@
       </c>
       <c r="I207" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>50-200</t>
         </is>
       </c>
       <c r="J207" s="18" t="inlineStr">
         <is>
-          <t>UAV flight training; drone assembly courses</t>
+          <t>Agricultural drone spraying; pilot training services</t>
         </is>
       </c>
       <c r="K207" s="18" t="inlineStr">
         <is>
-          <t>Drone design and pilot simulation training</t>
+          <t>Precision agriculture drone spraying operations</t>
         </is>
       </c>
       <c r="L207" s="18" t="inlineStr">
         <is>
-          <t>Fixed-wing piloting; autopilot programming</t>
+          <t>DGCA-approved flight training; spraying drones</t>
         </is>
       </c>
       <c r="M207" s="15" t="inlineStr">
@@ -17867,14 +17867,22 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N207" s="18" t="inlineStr"/>
-      <c r="O207" s="18" t="inlineStr"/>
+      <c r="N207" s="18" t="inlineStr">
+        <is>
+          <t>Tamilarasu Kaliannan</t>
+        </is>
+      </c>
+      <c r="O207" s="18" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="P207" s="18" t="inlineStr"/>
       <c r="Q207" s="18" t="inlineStr"/>
       <c r="R207" s="18" t="inlineStr"/>
       <c r="S207" s="17" t="inlineStr">
         <is>
-          <t>maavandrones.com</t>
+          <t>aeroticstechnologies.com</t>
         </is>
       </c>
       <c r="T207" s="18" t="inlineStr"/>
@@ -17884,18 +17892,18 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="33" customHeight="1">
+    <row r="208" ht="46.5" customHeight="1">
       <c r="A208" s="11" t="n">
         <v>203</v>
       </c>
       <c r="B208" s="12" t="inlineStr">
         <is>
-          <t>Aerotics Technologies LLP</t>
+          <t>Hawking UAV</t>
         </is>
       </c>
       <c r="C208" s="13" t="inlineStr">
         <is>
-          <t>aeroticstechnologies.com</t>
+          <t>http://hawking.in</t>
         </is>
       </c>
       <c r="D208" s="11" t="n">
@@ -17903,7 +17911,7 @@
       </c>
       <c r="E208" s="14" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F208" s="14" t="inlineStr">
@@ -17923,22 +17931,22 @@
       </c>
       <c r="I208" s="11" t="inlineStr">
         <is>
-          <t>50-200</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>Agricultural drone spraying; pilot training services</t>
+          <t>Drone survey and mapping; Agricultural spraying; Thermal inspection</t>
         </is>
       </c>
       <c r="K208" s="14" t="inlineStr">
         <is>
-          <t>Precision agriculture drone spraying operations</t>
+          <t>UAS-based solutions for oil and pipeline inspection, utility mapping, and wildlife management</t>
         </is>
       </c>
       <c r="L208" s="14" t="inlineStr">
         <is>
-          <t>DGCA-approved flight training; spraying drones</t>
+          <t>LiDAR and thermal sensors, onboard mission software, data processing analytics</t>
         </is>
       </c>
       <c r="M208" s="11" t="inlineStr">
@@ -17946,47 +17954,47 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N208" s="14" t="inlineStr">
-        <is>
-          <t>Tamilarasu Kaliannan</t>
-        </is>
-      </c>
-      <c r="O208" s="14" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+      <c r="N208" s="14" t="inlineStr"/>
+      <c r="O208" s="14" t="inlineStr"/>
       <c r="P208" s="14" t="inlineStr"/>
       <c r="Q208" s="14" t="inlineStr"/>
-      <c r="R208" s="14" t="inlineStr"/>
+      <c r="R208" s="14" t="inlineStr">
+        <is>
+          <t>+914447407452</t>
+        </is>
+      </c>
       <c r="S208" s="13" t="inlineStr">
         <is>
-          <t>aeroticstechnologies.com</t>
-        </is>
-      </c>
-      <c r="T208" s="14" t="inlineStr"/>
+          <t>http://hawking.in</t>
+        </is>
+      </c>
+      <c r="T208" s="13" t="inlineStr">
+        <is>
+          <t>info@hawking.in</t>
+        </is>
+      </c>
       <c r="U208" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="46.5" customHeight="1">
+    <row r="209" ht="33" customHeight="1">
       <c r="A209" s="15" t="n">
         <v>204</v>
       </c>
       <c r="B209" s="16" t="inlineStr">
         <is>
-          <t>Hawking UAV</t>
+          <t>Geo Adithya Technologies</t>
         </is>
       </c>
       <c r="C209" s="17" t="inlineStr">
         <is>
-          <t>http://hawking.in</t>
+          <t>geoadithya.com</t>
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="E209" s="18" t="inlineStr">
         <is>
@@ -18015,17 +18023,17 @@
       </c>
       <c r="J209" s="18" t="inlineStr">
         <is>
-          <t>Drone survey and mapping; Agricultural spraying; Thermal inspection</t>
+          <t>UAV drone services; GIS mapping; Topographical survey</t>
         </is>
       </c>
       <c r="K209" s="18" t="inlineStr">
         <is>
-          <t>UAS-based solutions for oil and pipeline inspection, utility mapping, and wildlife management</t>
+          <t>Geospatial data capture and high-resolution aerial imaging solutions</t>
         </is>
       </c>
       <c r="L209" s="18" t="inlineStr">
         <is>
-          <t>LiDAR and thermal sensors, onboard mission software, data processing analytics</t>
+          <t>Drone photogrammetry, GIS modeling, total station integration</t>
         </is>
       </c>
       <c r="M209" s="15" t="inlineStr">
@@ -18033,23 +18041,35 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N209" s="18" t="inlineStr"/>
-      <c r="O209" s="18" t="inlineStr"/>
-      <c r="P209" s="18" t="inlineStr"/>
+      <c r="N209" s="18" t="inlineStr">
+        <is>
+          <t>Khushi Khatri</t>
+        </is>
+      </c>
+      <c r="O209" s="18" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="P209" s="17" t="inlineStr">
+        <is>
+          <t>bdm2@geoadithya.com</t>
+        </is>
+      </c>
       <c r="Q209" s="18" t="inlineStr"/>
       <c r="R209" s="18" t="inlineStr">
         <is>
-          <t>+914447407452</t>
+          <t>+918608877766</t>
         </is>
       </c>
       <c r="S209" s="17" t="inlineStr">
         <is>
-          <t>http://hawking.in</t>
+          <t>geoadithya.com</t>
         </is>
       </c>
       <c r="T209" s="17" t="inlineStr">
         <is>
-          <t>info@hawking.in</t>
+          <t>info@geoadithya.com</t>
         </is>
       </c>
       <c r="U209" s="15" t="inlineStr">
@@ -18064,20 +18084,20 @@
       </c>
       <c r="B210" s="12" t="inlineStr">
         <is>
-          <t>Geo Adithya Technologies</t>
+          <t>Magizh Engineering Services</t>
         </is>
       </c>
       <c r="C210" s="13" t="inlineStr">
         <is>
-          <t>geoadithya.com</t>
+          <t>https://magzhiengineering.weebly.com</t>
         </is>
       </c>
       <c r="D210" s="11" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="F210" s="14" t="inlineStr">
@@ -18092,157 +18112,59 @@
       </c>
       <c r="H210" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Joint Venture</t>
         </is>
       </c>
       <c r="I210" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>UAV drone services; GIS mapping; Topographical survey</t>
+          <t>Drone aerial mapping; industrial inspection services</t>
         </is>
       </c>
       <c r="K210" s="14" t="inlineStr">
         <is>
-          <t>Geospatial data capture and high-resolution aerial imaging solutions</t>
+          <t>Engineering-grade drone land surveying and mapping</t>
         </is>
       </c>
       <c r="L210" s="14" t="inlineStr">
         <is>
-          <t>Drone photogrammetry, GIS modeling, total station integration</t>
+          <t>UAV mapping sensors, industrial CAD modeling based on drone data</t>
         </is>
       </c>
       <c r="M210" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N210" s="14" t="inlineStr">
-        <is>
-          <t>Khushi Khatri</t>
-        </is>
-      </c>
-      <c r="O210" s="14" t="inlineStr">
-        <is>
-          <t>Business Development Manager</t>
-        </is>
-      </c>
-      <c r="P210" s="13" t="inlineStr">
-        <is>
-          <t>bdm2@geoadithya.com</t>
-        </is>
-      </c>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N210" s="14" t="inlineStr"/>
+      <c r="O210" s="14" t="inlineStr"/>
+      <c r="P210" s="14" t="inlineStr"/>
       <c r="Q210" s="14" t="inlineStr"/>
-      <c r="R210" s="14" t="inlineStr">
-        <is>
-          <t>+918608877766</t>
-        </is>
-      </c>
+      <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="13" t="inlineStr">
         <is>
-          <t>geoadithya.com</t>
-        </is>
-      </c>
-      <c r="T210" s="13" t="inlineStr">
-        <is>
-          <t>info@geoadithya.com</t>
-        </is>
-      </c>
+          <t>https://magzhiengineering.weebly.com</t>
+        </is>
+      </c>
+      <c r="T210" s="14" t="inlineStr"/>
       <c r="U210" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="33" customHeight="1">
-      <c r="A211" s="15" t="n">
-        <v>206</v>
-      </c>
-      <c r="B211" s="16" t="inlineStr">
-        <is>
-          <t>Magizh Engineering Services</t>
-        </is>
-      </c>
-      <c r="C211" s="17" t="inlineStr">
-        <is>
-          <t>https://magzhiengineering.weebly.com</t>
-        </is>
-      </c>
-      <c r="D211" s="15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E211" s="18" t="inlineStr">
-        <is>
-          <t>Coimbatore, India</t>
-        </is>
-      </c>
-      <c r="F211" s="18" t="inlineStr">
-        <is>
-          <t>APAC(India)</t>
-        </is>
-      </c>
-      <c r="G211" s="18" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H211" s="18" t="inlineStr">
-        <is>
-          <t>Joint Venture</t>
-        </is>
-      </c>
-      <c r="I211" s="15" t="inlineStr">
-        <is>
-          <t>1-10</t>
-        </is>
-      </c>
-      <c r="J211" s="18" t="inlineStr">
-        <is>
-          <t>Drone aerial mapping; industrial inspection services</t>
-        </is>
-      </c>
-      <c r="K211" s="18" t="inlineStr">
-        <is>
-          <t>Engineering-grade drone land surveying and mapping</t>
-        </is>
-      </c>
-      <c r="L211" s="18" t="inlineStr">
-        <is>
-          <t>UAV mapping sensors, industrial CAD modeling based on drone data</t>
-        </is>
-      </c>
-      <c r="M211" s="15" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N211" s="18" t="inlineStr"/>
-      <c r="O211" s="18" t="inlineStr"/>
-      <c r="P211" s="18" t="inlineStr"/>
-      <c r="Q211" s="18" t="inlineStr"/>
-      <c r="R211" s="18" t="inlineStr"/>
-      <c r="S211" s="17" t="inlineStr">
-        <is>
-          <t>https://magzhiengineering.weebly.com</t>
-        </is>
-      </c>
-      <c r="T211" s="18" t="inlineStr"/>
-      <c r="U211" s="15" t="inlineStr">
-        <is>
-          <t>+91 / IN</t>
-        </is>
-      </c>
-    </row>
+    <row r="211" ht="29" customHeight="1"/>
     <row r="212" ht="29" customHeight="1"/>
     <row r="213" ht="42" customHeight="1"/>
     <row r="214" ht="29" customHeight="1"/>
     <row r="215" ht="29" customHeight="1"/>
     <row r="216" ht="42" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A5:U211"/>
+  <autoFilter ref="A5:U210"/>
   <mergeCells count="4">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A4:U4"/>
@@ -18559,29 +18481,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId307"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T135" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T136" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T137" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T138" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T139" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T140" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T134" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T135" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T136" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T137" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T138" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T139" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId333"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId335"/>
@@ -18591,107 +18513,107 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId339"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T145" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId355"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId357"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId359"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T154" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId373"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T158" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T159" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T158" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId385"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId393"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId403"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId413"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId415"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId416"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId417"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T176" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T177" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T175" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T176" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId425"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P179" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T179" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P178" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T178" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId431"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId432"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId433"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId434"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId435"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P183" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P184" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P182" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P183" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId443"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId445"/>
@@ -18701,27 +18623,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId449"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId450"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S188" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T189" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T188" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S190" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T191" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T190" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId459"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId461"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId462"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId463"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T195" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P196" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T196" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T194" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P195" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T195" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId472"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId473"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId475"/>
@@ -18729,14 +18651,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S199" r:id="rId478"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P201" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T201" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T202" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P200" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T200" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T201" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId487"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId488"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S203" r:id="rId489"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId490"/>
@@ -18749,15 +18671,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S207" r:id="rId497"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId498"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S208" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S209" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T209" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P210" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S210" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T210" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S211" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T208" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P209" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S209" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T209" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S210" r:id="rId506"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
